--- a/backtest_df.xlsx
+++ b/backtest_df.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M121"/>
+  <dimension ref="A1:M122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,11 +499,11 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45688</v>
+        <v>45692</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NSE:FSL-EQ</t>
+          <t>NSE:CAMPUS-EQ</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -512,22 +512,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="F2" t="n">
-        <v>335.15</v>
+        <v>277.2</v>
       </c>
       <c r="G2" t="n">
-        <v>40553.14999999999</v>
+        <v>36867.6</v>
       </c>
       <c r="H2" t="n">
-        <v>40.55315</v>
+        <v>36.8676</v>
       </c>
       <c r="I2" t="n">
-        <v>20.276575</v>
+        <v>18.4338</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8162342969497933</v>
+        <v>0.7423928571428572</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -538,11 +538,11 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45688</v>
+        <v>45692</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NSE:GOKULAGRO-EQ</t>
+          <t>NSE:FORTIS-EQ</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>121</v>
+        <v>58</v>
       </c>
       <c r="F3" t="n">
-        <v>309.05</v>
+        <v>629.05</v>
       </c>
       <c r="G3" t="n">
-        <v>37395.05</v>
+        <v>36484.89999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>37.39505</v>
+        <v>36.4849</v>
       </c>
       <c r="I3" t="n">
-        <v>18.697525</v>
+        <v>18.24245</v>
       </c>
       <c r="J3" t="n">
-        <v>0.750696740076412</v>
+        <v>0.7364166666666666</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -577,11 +577,11 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45688</v>
+        <v>45692</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NSE:SARDAEN-EQ</t>
+          <t>NSE:PNBHOUSING-EQ</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -590,22 +590,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="F4" t="n">
-        <v>473.2</v>
+        <v>868.85</v>
       </c>
       <c r="G4" t="n">
-        <v>39748.8</v>
+        <v>36491.7</v>
       </c>
       <c r="H4" t="n">
-        <v>39.7488</v>
+        <v>36.4917</v>
       </c>
       <c r="I4" t="n">
-        <v>19.8744</v>
+        <v>18.24585</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7952736119665004</v>
+        <v>0.7427579365079366</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -616,11 +616,11 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45689</v>
+        <v>45692</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NSE:MCX-EQ</t>
+          <t>NSE:RALLIS-EQ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -629,22 +629,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>155</v>
       </c>
       <c r="F5" t="n">
-        <v>5774.75</v>
+        <v>236.65</v>
       </c>
       <c r="G5" t="n">
-        <v>34648.5</v>
+        <v>36680.75</v>
       </c>
       <c r="H5" t="n">
-        <v>34.6485</v>
+        <v>36.68075</v>
       </c>
       <c r="I5" t="n">
-        <v>17.32425</v>
+        <v>18.340375</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8052505485903635</v>
+        <v>0.7351071428571428</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -655,11 +655,11 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45689</v>
+        <v>45693</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NSE:SKYGOLD-EQ</t>
+          <t>NSE:CESC-EQ</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -668,22 +668,22 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>128</v>
+        <v>265</v>
       </c>
       <c r="F6" t="n">
-        <v>331.5</v>
+        <v>139.47</v>
       </c>
       <c r="G6" t="n">
-        <v>42432</v>
+        <v>36959.55</v>
       </c>
       <c r="H6" t="n">
-        <v>42.432</v>
+        <v>36.95955000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>21.216</v>
+        <v>18.479775</v>
       </c>
       <c r="J6" t="n">
-        <v>0.852943708679353</v>
+        <v>0.7401150793650794</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -694,11 +694,11 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45691</v>
+        <v>45693</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NSE:DIXON-EQ</t>
+          <t>NSE:GICRE-EQ</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -707,22 +707,22 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>94</v>
       </c>
       <c r="F7" t="n">
-        <v>14486.15</v>
+        <v>408.1</v>
       </c>
       <c r="G7" t="n">
-        <v>28972.3</v>
+        <v>38361.4</v>
       </c>
       <c r="H7" t="n">
-        <v>28.9723</v>
+        <v>38.3614</v>
       </c>
       <c r="I7" t="n">
-        <v>14.48615</v>
+        <v>19.1807</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7818051286249024</v>
+        <v>0.7696785714285714</v>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -733,11 +733,11 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45691</v>
+        <v>45693</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NSE:INDHOTEL-EQ</t>
+          <t>NSE:SEQUENT-EQ</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -746,22 +746,22 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>48</v>
+        <v>223</v>
       </c>
       <c r="F8" t="n">
-        <v>816.2</v>
+        <v>164.36</v>
       </c>
       <c r="G8" t="n">
-        <v>39177.60000000001</v>
+        <v>36652.28000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>39.17760000000001</v>
+        <v>36.65228</v>
       </c>
       <c r="I8" t="n">
-        <v>19.5888</v>
+        <v>18.32614</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7880570295141276</v>
+        <v>0.733888888888889</v>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -772,54 +772,50 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45691</v>
+        <v>45694</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NSE:SARDAEN-EQ</t>
+          <t>NSE:AVANTIFEED-EQ</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="F9" t="n">
-        <v>446.05</v>
+        <v>729.1</v>
       </c>
       <c r="G9" t="n">
-        <v>37468.2</v>
+        <v>36455</v>
       </c>
       <c r="H9" t="n">
-        <v>37.4682</v>
+        <v>36.455</v>
       </c>
       <c r="I9" t="n">
-        <v>18.7341</v>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="n">
-        <v>-2336.802299999993</v>
-      </c>
-      <c r="L9" t="n">
-        <v>-5.737531699070145</v>
-      </c>
-      <c r="M9" t="n">
-        <v>473.1999999999999</v>
-      </c>
+        <v>18.2275</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.7411031746031747</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45691</v>
+        <v>45698</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NSE:ZAGGLE-EQ</t>
+          <t>NSE:ALEMBICLTD-EQ</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -828,22 +824,22 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>86</v>
+        <v>332</v>
       </c>
       <c r="F10" t="n">
-        <v>449</v>
+        <v>111.67</v>
       </c>
       <c r="G10" t="n">
-        <v>38614</v>
+        <v>37074.44</v>
       </c>
       <c r="H10" t="n">
-        <v>38.614</v>
+        <v>37.07444</v>
       </c>
       <c r="I10" t="n">
-        <v>19.307</v>
+        <v>18.53722</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7792177517155743</v>
+        <v>0.7430198412698412</v>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
@@ -854,50 +850,54 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45691</v>
+        <v>45699</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NSE:ZUARI-EQ</t>
+          <t>NSE:ALEMBICLTD-EQ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>212</v>
+        <v>332</v>
       </c>
       <c r="F11" t="n">
-        <v>197.65</v>
+        <v>105.62</v>
       </c>
       <c r="G11" t="n">
-        <v>41901.8</v>
+        <v>35065.84</v>
       </c>
       <c r="H11" t="n">
-        <v>41.9018</v>
+        <v>35.06584</v>
       </c>
       <c r="I11" t="n">
-        <v>20.9509</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.8389136985572692</v>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+        <v>17.53292</v>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="n">
+        <v>-2061.198759999999</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-5.417748723918686</v>
+      </c>
+      <c r="M11" t="n">
+        <v>111.67</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45692</v>
+        <v>45699</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NSE:ASHOKA-EQ</t>
+          <t>NSE:AMBUJACEM-EQ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -906,22 +906,22 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>156</v>
+        <v>75</v>
       </c>
       <c r="F12" t="n">
-        <v>242.8</v>
+        <v>499.9</v>
       </c>
       <c r="G12" t="n">
-        <v>37876.8</v>
+        <v>37492.5</v>
       </c>
       <c r="H12" t="n">
-        <v>37.8768</v>
+        <v>37.4925</v>
       </c>
       <c r="I12" t="n">
-        <v>18.9384</v>
+        <v>18.74625</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7600805930255063</v>
+        <v>0.7582182539682539</v>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -932,89 +932,97 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45692</v>
+        <v>45699</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NSE:BANCOINDIA-EQ</t>
+          <t>NSE:CAMPUS-EQ</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>90</v>
+        <v>133</v>
       </c>
       <c r="F13" t="n">
-        <v>448.6</v>
+        <v>262.3</v>
       </c>
       <c r="G13" t="n">
-        <v>40374</v>
+        <v>34885.9</v>
       </c>
       <c r="H13" t="n">
-        <v>40.374</v>
+        <v>34.8859</v>
       </c>
       <c r="I13" t="n">
-        <v>20.187</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.8160727428349374</v>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+        <v>17.44295</v>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="n">
+        <v>-2034.028849999997</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-5.375180375180367</v>
+      </c>
+      <c r="M13" t="n">
+        <v>277.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45692</v>
+        <v>45699</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NSE:RADICO-EQ</t>
+          <t>NSE:GICRE-EQ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="F14" t="n">
-        <v>2304.9</v>
+        <v>380.85</v>
       </c>
       <c r="G14" t="n">
-        <v>36878.4</v>
+        <v>35799.9</v>
       </c>
       <c r="H14" t="n">
-        <v>36.8784</v>
+        <v>35.7999</v>
       </c>
       <c r="I14" t="n">
-        <v>18.4392</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.7667586077947878</v>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+        <v>17.89995</v>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="n">
+        <v>-2615.19985</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-6.677284979171771</v>
+      </c>
+      <c r="M14" t="n">
+        <v>408.1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45692</v>
+        <v>45699</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NSE:WELCORP-EQ</t>
+          <t>NSE:MAZDOCK-EQ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1023,22 +1031,22 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="F15" t="n">
-        <v>720.35</v>
+        <v>2185.2</v>
       </c>
       <c r="G15" t="n">
-        <v>38178.55</v>
+        <v>37148.39999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>38.17855</v>
+        <v>37.1484</v>
       </c>
       <c r="I15" t="n">
-        <v>19.089275</v>
+        <v>18.5742</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7778886853163907</v>
+        <v>0.7430238095238095</v>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
@@ -1049,50 +1057,54 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45693</v>
+        <v>45700</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NSE:NIITLTD-EQ</t>
+          <t>NSE:PNBHOUSING-EQ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>267</v>
+        <v>42</v>
       </c>
       <c r="F16" t="n">
-        <v>147.34</v>
+        <v>818.7</v>
       </c>
       <c r="G16" t="n">
-        <v>39339.78</v>
+        <v>34385.4</v>
       </c>
       <c r="H16" t="n">
-        <v>39.33978</v>
+        <v>34.3854</v>
       </c>
       <c r="I16" t="n">
-        <v>19.66989</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.7879414799738987</v>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+        <v>17.1927</v>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="n">
+        <v>-2157.878100000004</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-5.771997467917371</v>
+      </c>
+      <c r="M16" t="n">
+        <v>868.8500000000001</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45693</v>
+        <v>45701</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NSE:SKYGOLD-EQ</t>
+          <t>NSE:RALLIS-EQ</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1101,29 +1113,29 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="F17" t="n">
-        <v>383.7</v>
+        <v>223.69</v>
       </c>
       <c r="G17" t="n">
-        <v>49113.6</v>
+        <v>34671.95</v>
       </c>
       <c r="H17" t="n">
-        <v>49.1136</v>
+        <v>34.67195</v>
       </c>
       <c r="I17" t="n">
-        <v>24.5568</v>
+        <v>17.335975</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="n">
-        <v>6607.929599999999</v>
+        <v>-2060.807925000001</v>
       </c>
       <c r="L17" t="n">
-        <v>15.74660633484163</v>
+        <v>-5.476442002957958</v>
       </c>
       <c r="M17" t="n">
-        <v>331.5</v>
+        <v>236.65</v>
       </c>
     </row>
     <row r="18">
@@ -1131,179 +1143,171 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45694</v>
+        <v>45702</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NSE:COFORGE-EQ</t>
+          <t>NSE:AVANTIFEED-EQ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F18" t="n">
-        <v>1704.27</v>
+        <v>659</v>
       </c>
       <c r="G18" t="n">
-        <v>42606.75</v>
+        <v>32950</v>
       </c>
       <c r="H18" t="n">
-        <v>42.60675</v>
+        <v>32.95</v>
       </c>
       <c r="I18" t="n">
-        <v>21.303375</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.8775904236070656</v>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+        <v>16.475</v>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="n">
+        <v>-3554.425000000001</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-9.614593334247704</v>
+      </c>
+      <c r="M18" t="n">
+        <v>729.1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
         <v>17</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45698</v>
+        <v>45702</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NSE:ZAGGLE-EQ</t>
+          <t>NSE:BORORENEW-EQ</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="F19" t="n">
-        <v>424.05</v>
+        <v>497.3</v>
       </c>
       <c r="G19" t="n">
-        <v>36468.3</v>
+        <v>36302.9</v>
       </c>
       <c r="H19" t="n">
-        <v>36.46830000000001</v>
+        <v>36.3029</v>
       </c>
       <c r="I19" t="n">
-        <v>18.23415</v>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="n">
-        <v>-2200.402449999999</v>
-      </c>
-      <c r="L19" t="n">
-        <v>-5.556792873051222</v>
-      </c>
-      <c r="M19" t="n">
-        <v>449</v>
-      </c>
+        <v>18.15145</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.7319404761904761</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
         <v>18</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45699</v>
+        <v>45702</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NSE:GOKULAGRO-EQ</t>
+          <t>NSE:INDIANB-EQ</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="F20" t="n">
-        <v>292.95</v>
+        <v>508.45</v>
       </c>
       <c r="G20" t="n">
-        <v>35446.95</v>
+        <v>39659.1</v>
       </c>
       <c r="H20" t="n">
-        <v>35.44695</v>
+        <v>39.6591</v>
       </c>
       <c r="I20" t="n">
-        <v>17.723475</v>
-      </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="n">
-        <v>-2001.270425000003</v>
-      </c>
-      <c r="L20" t="n">
-        <v>-5.209513023782566</v>
-      </c>
-      <c r="M20" t="n">
-        <v>309.05</v>
-      </c>
+        <v>19.82955</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.7999206349206347</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
         <v>19</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45699</v>
+        <v>45702</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NSE:INDHOTEL-EQ</t>
+          <t>NSE:MEDIASSIST-EQ</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="F21" t="n">
-        <v>748</v>
+        <v>490.75</v>
       </c>
       <c r="G21" t="n">
-        <v>35904</v>
+        <v>36806.25</v>
       </c>
       <c r="H21" t="n">
-        <v>35.904</v>
+        <v>36.80625</v>
       </c>
       <c r="I21" t="n">
-        <v>17.952</v>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="n">
-        <v>-3327.456000000008</v>
-      </c>
-      <c r="L21" t="n">
-        <v>-8.355795148247996</v>
-      </c>
-      <c r="M21" t="n">
-        <v>816.2000000000002</v>
-      </c>
+        <v>18.403125</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.7376190476190477</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
         <v>20</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45699</v>
+        <v>45702</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NSE:SHARDACROP-EQ</t>
+          <t>NSE:PHOENIXLTD-EQ</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1312,22 +1316,22 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="F22" t="n">
-        <v>559.7</v>
+        <v>1569.6</v>
       </c>
       <c r="G22" t="n">
-        <v>42537.2</v>
+        <v>37670.39999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>42.53720000000001</v>
+        <v>37.67039999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>21.2686</v>
+        <v>18.8352</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8542075515023626</v>
+        <v>0.7686388888888891</v>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
@@ -1338,175 +1342,175 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>45699</v>
+        <v>45702</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NSE:SUMICHEM-EQ</t>
+          <t>NSE:SEQUENT-EQ</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>78</v>
+        <v>223</v>
       </c>
       <c r="F23" t="n">
-        <v>492.35</v>
+        <v>146.52</v>
       </c>
       <c r="G23" t="n">
-        <v>38403.3</v>
+        <v>32673.96</v>
       </c>
       <c r="H23" t="n">
-        <v>38.4033</v>
+        <v>32.67396</v>
       </c>
       <c r="I23" t="n">
-        <v>19.20165</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.7746774161486728</v>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+        <v>16.33698</v>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="n">
+        <v>-4027.330940000001</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-10.85422243854953</v>
+      </c>
+      <c r="M23" t="n">
+        <v>164.36</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
         <v>22</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>45700</v>
+        <v>45702</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NSE:COFORGE-EQ</t>
+          <t>NSE:SHRIRAMFIN-EQ</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="F24" t="n">
-        <v>1600.88</v>
+        <v>539.15</v>
       </c>
       <c r="G24" t="n">
-        <v>40022</v>
+        <v>37201.35</v>
       </c>
       <c r="H24" t="n">
-        <v>40.022</v>
+        <v>37.20135</v>
       </c>
       <c r="I24" t="n">
-        <v>20.011</v>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="n">
-        <v>-2644.782999999997</v>
-      </c>
-      <c r="L24" t="n">
-        <v>-6.066527017432676</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1704.27</v>
-      </c>
+        <v>18.600675</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.7473373015873015</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
         <v>23</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>45700</v>
+        <v>45705</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NSE:SKYGOLD-EQ</t>
+          <t>NSE:CESC-EQ</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106</v>
+        <v>265</v>
       </c>
       <c r="F25" t="n">
-        <v>358.65</v>
+        <v>125.92</v>
       </c>
       <c r="G25" t="n">
-        <v>38016.89999999999</v>
+        <v>33368.8</v>
       </c>
       <c r="H25" t="n">
-        <v>38.01689999999999</v>
+        <v>33.3688</v>
       </c>
       <c r="I25" t="n">
-        <v>19.00845</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.7664966104836256</v>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+        <v>16.6844</v>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="n">
+        <v>-3640.803199999999</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-9.715350971535095</v>
+      </c>
+      <c r="M25" t="n">
+        <v>139.47</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
         <v>24</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>45701</v>
+        <v>45706</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NSE:RADICO-EQ</t>
+          <t>NSE:MCX-EQ</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F26" t="n">
-        <v>2125.2</v>
+        <v>5438.4</v>
       </c>
       <c r="G26" t="n">
-        <v>34003.2</v>
+        <v>38068.8</v>
       </c>
       <c r="H26" t="n">
-        <v>34.0032</v>
+        <v>38.0688</v>
       </c>
       <c r="I26" t="n">
-        <v>17.0016</v>
-      </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="n">
-        <v>-2926.204800000005</v>
-      </c>
-      <c r="L26" t="n">
-        <v>-7.796433684758569</v>
-      </c>
-      <c r="M26" t="n">
-        <v>2304.9</v>
-      </c>
+        <v>19.0344</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.7900595238095238</v>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
         <v>25</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>45701</v>
+        <v>45709</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NSE:SARDAEN-EQ</t>
+          <t>NSE:COROMANDEL-EQ</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1515,22 +1519,22 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="F27" t="n">
-        <v>461.25</v>
+        <v>1708.5</v>
       </c>
       <c r="G27" t="n">
-        <v>37361.25</v>
+        <v>39295.5</v>
       </c>
       <c r="H27" t="n">
-        <v>37.36125</v>
+        <v>39.2955</v>
       </c>
       <c r="I27" t="n">
-        <v>18.680625</v>
+        <v>19.64775</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7556595454269156</v>
+        <v>0.8166547619047618</v>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
@@ -1541,179 +1545,171 @@
         <v>26</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>45702</v>
+        <v>45709</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>NSE:MCX-EQ</t>
+          <t>NSE:ELGIEQUIP-EQ</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="F28" t="n">
-        <v>5443.7</v>
+        <v>476.6</v>
       </c>
       <c r="G28" t="n">
-        <v>32662.2</v>
+        <v>36221.6</v>
       </c>
       <c r="H28" t="n">
-        <v>32.6622</v>
+        <v>36.2216</v>
       </c>
       <c r="I28" t="n">
-        <v>16.3311</v>
-      </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="n">
-        <v>-2035.293300000001</v>
-      </c>
-      <c r="L28" t="n">
-        <v>-5.732715701978443</v>
-      </c>
-      <c r="M28" t="n">
-        <v>5774.75</v>
-      </c>
+        <v>18.1108</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.7319548229548228</v>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
         <v>27</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>45702</v>
+        <v>45709</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NSE:NIITLTD-EQ</t>
+          <t>NSE:JBCHEPHARM-EQ</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>267</v>
+        <v>23</v>
       </c>
       <c r="F29" t="n">
-        <v>124.72</v>
+        <v>1606.85</v>
       </c>
       <c r="G29" t="n">
-        <v>33300.24</v>
+        <v>36957.55</v>
       </c>
       <c r="H29" t="n">
-        <v>33.30024</v>
+        <v>36.95755</v>
       </c>
       <c r="I29" t="n">
-        <v>16.65012</v>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="n">
-        <v>-6089.490360000001</v>
-      </c>
-      <c r="L29" t="n">
-        <v>-15.35224650468305</v>
-      </c>
-      <c r="M29" t="n">
-        <v>147.34</v>
-      </c>
+        <v>18.478775</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.7683095238095238</v>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
         <v>28</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>45707</v>
+        <v>45713</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NSE:LTFOODS-EQ</t>
+          <t>NSE:FORTIS-EQ</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>101</v>
+        <v>58</v>
       </c>
       <c r="F30" t="n">
-        <v>385.5</v>
+        <v>608.35</v>
       </c>
       <c r="G30" t="n">
-        <v>38935.5</v>
+        <v>35284.3</v>
       </c>
       <c r="H30" t="n">
-        <v>38.9355</v>
+        <v>35.2843</v>
       </c>
       <c r="I30" t="n">
-        <v>19.46775</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.778957059516688</v>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+        <v>17.64215</v>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="n">
+        <v>-1253.526449999996</v>
+      </c>
+      <c r="L30" t="n">
+        <v>-3.290676416819002</v>
+      </c>
+      <c r="M30" t="n">
+        <v>629.05</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
         <v>29</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>45707</v>
+        <v>45715</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NSE:SKYGOLD-EQ</t>
+          <t>NSE:GRANULES-EQ</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="F31" t="n">
-        <v>337.7</v>
+        <v>506.95</v>
       </c>
       <c r="G31" t="n">
-        <v>35796.2</v>
+        <v>37007.35</v>
       </c>
       <c r="H31" t="n">
-        <v>35.7962</v>
+        <v>37.00735</v>
       </c>
       <c r="I31" t="n">
-        <v>17.8981</v>
-      </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="n">
-        <v>-2274.394299999993</v>
-      </c>
-      <c r="L31" t="n">
-        <v>-5.841349505088508</v>
-      </c>
-      <c r="M31" t="n">
-        <v>358.6499999999999</v>
-      </c>
+        <v>18.503675</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.7455862193362194</v>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
         <v>30</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>45709</v>
+        <v>45715</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NSE:ASHOKA-EQ</t>
+          <t>NSE:MEDIASSIST-EQ</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1722,29 +1718,29 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>156</v>
+        <v>75</v>
       </c>
       <c r="F32" t="n">
-        <v>195.6</v>
+        <v>462.2</v>
       </c>
       <c r="G32" t="n">
-        <v>30513.6</v>
+        <v>34665</v>
       </c>
       <c r="H32" t="n">
-        <v>30.5136</v>
+        <v>34.665</v>
       </c>
       <c r="I32" t="n">
-        <v>15.2568</v>
+        <v>17.3325</v>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="n">
-        <v>-7408.970400000003</v>
+        <v>-2193.247500000001</v>
       </c>
       <c r="L32" t="n">
-        <v>-19.43986820428337</v>
+        <v>-5.817626082526747</v>
       </c>
       <c r="M32" t="n">
-        <v>242.8</v>
+        <v>490.75</v>
       </c>
     </row>
     <row r="33">
@@ -1752,93 +1748,93 @@
         <v>31</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>45709</v>
+        <v>45715</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NSE:BANCOINDIA-EQ</t>
+          <t>NSE:PARAGMILK-EQ</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>90</v>
+        <v>255</v>
       </c>
       <c r="F33" t="n">
-        <v>325.25</v>
+        <v>152.82</v>
       </c>
       <c r="G33" t="n">
-        <v>29272.5</v>
+        <v>38969.1</v>
       </c>
       <c r="H33" t="n">
-        <v>29.2725</v>
+        <v>38.9691</v>
       </c>
       <c r="I33" t="n">
-        <v>14.63625</v>
-      </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="n">
-        <v>-11145.40875</v>
-      </c>
-      <c r="L33" t="n">
-        <v>-27.49665626393224</v>
-      </c>
-      <c r="M33" t="n">
-        <v>448.6</v>
-      </c>
+        <v>19.48455</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.7813571428571429</v>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
         <v>32</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>45709</v>
+        <v>45720</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>NSE:FORTIS-EQ</t>
+          <t>NSE:AMBUJACEM-EQ</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="F34" t="n">
-        <v>619.35</v>
+        <v>475</v>
       </c>
       <c r="G34" t="n">
-        <v>37780.35</v>
+        <v>35625</v>
       </c>
       <c r="H34" t="n">
-        <v>37.78035</v>
+        <v>35.625</v>
       </c>
       <c r="I34" t="n">
-        <v>18.890175</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0.7599602659132628</v>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
+        <v>17.8125</v>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="n">
+        <v>-1920.937499999998</v>
+      </c>
+      <c r="L34" t="n">
+        <v>-4.980996199239843</v>
+      </c>
+      <c r="M34" t="n">
+        <v>499.9</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
         <v>33</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>45709</v>
+        <v>45720</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NSE:FSL-EQ</t>
+          <t>NSE:COROMANDEL-EQ</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1847,29 +1843,29 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>121</v>
+        <v>23</v>
       </c>
       <c r="F35" t="n">
-        <v>368.05</v>
+        <v>1611.7</v>
       </c>
       <c r="G35" t="n">
-        <v>44534.05</v>
+        <v>37069.1</v>
       </c>
       <c r="H35" t="n">
-        <v>44.53405</v>
+        <v>37.0691</v>
       </c>
       <c r="I35" t="n">
-        <v>22.267025</v>
+        <v>18.53455</v>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="n">
-        <v>3914.098925000004</v>
+        <v>-2282.003649999999</v>
       </c>
       <c r="L35" t="n">
-        <v>9.816500074593476</v>
+        <v>-5.665788703541115</v>
       </c>
       <c r="M35" t="n">
-        <v>335.15</v>
+        <v>1708.5</v>
       </c>
     </row>
     <row r="36">
@@ -1877,93 +1873,93 @@
         <v>34</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>45709</v>
+        <v>45720</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NSE:GOKULAGRO-EQ</t>
+          <t>NSE:MAZDOCK-EQ</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>149</v>
+        <v>17</v>
       </c>
       <c r="F36" t="n">
-        <v>280.5</v>
+        <v>2162.5</v>
       </c>
       <c r="G36" t="n">
-        <v>41794.5</v>
+        <v>36762.5</v>
       </c>
       <c r="H36" t="n">
-        <v>41.7945</v>
+        <v>36.7625</v>
       </c>
       <c r="I36" t="n">
-        <v>20.89725</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0.8373208295719217</v>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
+        <v>18.38125</v>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="n">
+        <v>-441.0437499999969</v>
+      </c>
+      <c r="L36" t="n">
+        <v>-1.038806516565981</v>
+      </c>
+      <c r="M36" t="n">
+        <v>2185.2</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
         <v>35</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>45709</v>
+        <v>45721</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NSE:SHARDACROP-EQ</t>
+          <t>NSE:BEPL-EQ</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>76</v>
+        <v>355</v>
       </c>
       <c r="F37" t="n">
-        <v>531.35</v>
+        <v>104.62</v>
       </c>
       <c r="G37" t="n">
-        <v>40382.6</v>
+        <v>37140.1</v>
       </c>
       <c r="H37" t="n">
-        <v>40.3826</v>
+        <v>37.1401</v>
       </c>
       <c r="I37" t="n">
-        <v>20.1913</v>
-      </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="n">
-        <v>-2215.173900000002</v>
-      </c>
-      <c r="L37" t="n">
-        <v>-5.065213507236023</v>
-      </c>
-      <c r="M37" t="n">
-        <v>559.7</v>
-      </c>
+        <v>18.57005</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.744095238095238</v>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
         <v>36</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>45712</v>
+        <v>45721</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>NSE:DIXON-EQ</t>
+          <t>NSE:ELGIEQUIP-EQ</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1972,29 +1968,29 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2</v>
+        <v>76</v>
       </c>
       <c r="F38" t="n">
-        <v>14043.35</v>
+        <v>440.1</v>
       </c>
       <c r="G38" t="n">
-        <v>28086.7</v>
+        <v>33447.6</v>
       </c>
       <c r="H38" t="n">
-        <v>28.0867</v>
+        <v>33.4476</v>
       </c>
       <c r="I38" t="n">
-        <v>14.04335</v>
+        <v>16.7238</v>
       </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="n">
-        <v>-927.7300499999985</v>
+        <v>-2824.171399999996</v>
       </c>
       <c r="L38" t="n">
-        <v>-3.056712791183298</v>
+        <v>-7.658413764162808</v>
       </c>
       <c r="M38" t="n">
-        <v>14486.15</v>
+        <v>476.6</v>
       </c>
     </row>
     <row r="39">
@@ -2002,54 +1998,50 @@
         <v>37</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>45712</v>
+        <v>45721</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>NSE:ZUARI-EQ</t>
+          <t>NSE:FSL-EQ</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>212</v>
+        <v>104</v>
       </c>
       <c r="F39" t="n">
-        <v>188.81</v>
+        <v>361.15</v>
       </c>
       <c r="G39" t="n">
-        <v>40027.72</v>
+        <v>37559.6</v>
       </c>
       <c r="H39" t="n">
-        <v>40.02772</v>
+        <v>37.5596</v>
       </c>
       <c r="I39" t="n">
-        <v>20.01386</v>
-      </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="n">
-        <v>-1934.121580000001</v>
-      </c>
-      <c r="L39" t="n">
-        <v>-4.472552491778398</v>
-      </c>
-      <c r="M39" t="n">
-        <v>197.65</v>
-      </c>
+        <v>18.7798</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.7547738095238096</v>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
         <v>38</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>45713</v>
+        <v>45722</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NSE:FSL-EQ</t>
+          <t>NSE:JUBLFOOD-EQ</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2058,22 +2050,22 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>112</v>
+        <v>62</v>
       </c>
       <c r="F40" t="n">
-        <v>354.05</v>
+        <v>609.45</v>
       </c>
       <c r="G40" t="n">
-        <v>39653.6</v>
+        <v>37785.9</v>
       </c>
       <c r="H40" t="n">
-        <v>39.6536</v>
+        <v>37.78590000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>19.8268</v>
+        <v>18.89295</v>
       </c>
       <c r="J40" t="n">
-        <v>0.7980422015825823</v>
+        <v>0.7615833333333333</v>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
@@ -2084,50 +2076,54 @@
         <v>39</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>45713</v>
+        <v>45723</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NSE:LLOYDSME-EQ</t>
+          <t>NSE:BORORENEW-EQ</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="F41" t="n">
-        <v>1123.95</v>
+        <v>535.3</v>
       </c>
       <c r="G41" t="n">
-        <v>38214.3</v>
+        <v>39076.89999999999</v>
       </c>
       <c r="H41" t="n">
-        <v>38.2143</v>
+        <v>39.07689999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>19.10715</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0.7854539495211103</v>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
+        <v>19.53845</v>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="n">
+        <v>2715.384649999996</v>
+      </c>
+      <c r="L41" t="n">
+        <v>7.641262819223797</v>
+      </c>
+      <c r="M41" t="n">
+        <v>497.3</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
         <v>40</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>45713</v>
+        <v>45723</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NSE:LTFOODS-EQ</t>
+          <t>NSE:INDIANB-EQ</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2136,29 +2132,29 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="F42" t="n">
-        <v>357.2</v>
+        <v>530.15</v>
       </c>
       <c r="G42" t="n">
-        <v>36077.2</v>
+        <v>41351.7</v>
       </c>
       <c r="H42" t="n">
-        <v>36.0772</v>
+        <v>41.3517</v>
       </c>
       <c r="I42" t="n">
-        <v>18.0386</v>
+        <v>20.67585</v>
       </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="n">
-        <v>-2912.415800000001</v>
+        <v>1630.572449999999</v>
       </c>
       <c r="L42" t="n">
-        <v>-7.341115434500652</v>
+        <v>4.267872947192446</v>
       </c>
       <c r="M42" t="n">
-        <v>385.5</v>
+        <v>508.45</v>
       </c>
     </row>
     <row r="43">
@@ -2166,7 +2162,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>45713</v>
+        <v>45723</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -2175,162 +2171,170 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F43" t="n">
-        <v>5497.55</v>
+        <v>4664.05</v>
       </c>
       <c r="G43" t="n">
-        <v>32985.3</v>
+        <v>32648.35</v>
       </c>
       <c r="H43" t="n">
-        <v>32.9853</v>
+        <v>32.64835</v>
       </c>
       <c r="I43" t="n">
-        <v>16.49265</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0.7660510759149727</v>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
+        <v>16.324175</v>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="n">
+        <v>-5469.422524999996</v>
+      </c>
+      <c r="L43" t="n">
+        <v>-14.23856281259193</v>
+      </c>
+      <c r="M43" t="n">
+        <v>5438.4</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
         <v>42</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>45713</v>
+        <v>45723</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NSE:SAREGAMA-EQ</t>
+          <t>NSE:PHOENIXLTD-EQ</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>85</v>
+        <v>24</v>
       </c>
       <c r="F44" t="n">
-        <v>497.15</v>
+        <v>1560.15</v>
       </c>
       <c r="G44" t="n">
-        <v>42257.75</v>
+        <v>37443.60000000001</v>
       </c>
       <c r="H44" t="n">
-        <v>42.25775</v>
+        <v>37.4436</v>
       </c>
       <c r="I44" t="n">
-        <v>21.128875</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0.8455286476802858</v>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
+        <v>18.7218</v>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="n">
+        <v>-282.9653999999902</v>
+      </c>
+      <c r="L44" t="n">
+        <v>-0.6020642201834603</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1569.6</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
         <v>43</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>45713</v>
+        <v>45726</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NSE:WELCORP-EQ</t>
+          <t>NSE:CGCL-EQ</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>53</v>
+        <v>253</v>
       </c>
       <c r="F45" t="n">
-        <v>762.35</v>
+        <v>159.61</v>
       </c>
       <c r="G45" t="n">
-        <v>40404.55</v>
+        <v>40381.33</v>
       </c>
       <c r="H45" t="n">
-        <v>40.40455</v>
+        <v>40.38133000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>20.202275</v>
-      </c>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="n">
-        <v>2165.393175</v>
-      </c>
-      <c r="L45" t="n">
-        <v>5.830499062955507</v>
-      </c>
-      <c r="M45" t="n">
-        <v>720.35</v>
-      </c>
+        <v>20.190665</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.8094722222222223</v>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
         <v>44</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>45715</v>
+        <v>45726</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NSE:PGEL-EQ</t>
+          <t>NSE:FSL-EQ</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>47</v>
+        <v>104</v>
       </c>
       <c r="F46" t="n">
-        <v>794.85</v>
+        <v>340.05</v>
       </c>
       <c r="G46" t="n">
-        <v>37357.95</v>
+        <v>35365.2</v>
       </c>
       <c r="H46" t="n">
-        <v>37.35795</v>
+        <v>35.36520000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>18.678975</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0.7541055294629867</v>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
+        <v>17.6826</v>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="n">
+        <v>-2247.447799999996</v>
+      </c>
+      <c r="L46" t="n">
+        <v>-5.84244773639761</v>
+      </c>
+      <c r="M46" t="n">
+        <v>361.15</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
         <v>45</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>45716</v>
+        <v>45726</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>NSE:SUMICHEM-EQ</t>
+          <t>NSE:GRANULES-EQ</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2339,29 +2343,29 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="F47" t="n">
-        <v>460.6</v>
+        <v>478.65</v>
       </c>
       <c r="G47" t="n">
-        <v>35926.8</v>
+        <v>34941.45</v>
       </c>
       <c r="H47" t="n">
-        <v>35.92680000000001</v>
+        <v>34.94145</v>
       </c>
       <c r="I47" t="n">
-        <v>17.9634</v>
+        <v>17.470725</v>
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="n">
-        <v>-2530.3902</v>
+        <v>-2118.312175000001</v>
       </c>
       <c r="L47" t="n">
-        <v>-6.448664567888697</v>
+        <v>-5.582404576388207</v>
       </c>
       <c r="M47" t="n">
-        <v>492.35</v>
+        <v>506.95</v>
       </c>
     </row>
     <row r="48">
@@ -2369,50 +2373,54 @@
         <v>46</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>45719</v>
+        <v>45726</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NSE:EPACK-EQ</t>
+          <t>NSE:SHRIRAMFIN-EQ</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>109</v>
+        <v>69</v>
       </c>
       <c r="F48" t="n">
-        <v>358.8</v>
+        <v>625.6</v>
       </c>
       <c r="G48" t="n">
-        <v>39109.2</v>
+        <v>43166.4</v>
       </c>
       <c r="H48" t="n">
-        <v>39.10920000000001</v>
+        <v>43.1664</v>
       </c>
       <c r="I48" t="n">
-        <v>19.5546</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0.7876934113417355</v>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
+        <v>21.5832</v>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="n">
+        <v>5900.300400000003</v>
+      </c>
+      <c r="L48" t="n">
+        <v>16.03449874802931</v>
+      </c>
+      <c r="M48" t="n">
+        <v>539.15</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
         <v>47</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>45719</v>
+        <v>45728</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>NSE:REFEX-EQ</t>
+          <t>NSE:AVALON-EQ</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2421,22 +2429,22 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="F49" t="n">
-        <v>379.7</v>
+        <v>680.65</v>
       </c>
       <c r="G49" t="n">
-        <v>38729.4</v>
+        <v>38797.05</v>
       </c>
       <c r="H49" t="n">
-        <v>38.72940000000001</v>
+        <v>38.79705</v>
       </c>
       <c r="I49" t="n">
-        <v>19.3647</v>
+        <v>19.398525</v>
       </c>
       <c r="J49" t="n">
-        <v>0.7761723618536691</v>
+        <v>0.7762023809523809</v>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
@@ -2447,97 +2455,89 @@
         <v>48</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>45721</v>
+        <v>45728</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>NSE:GOKULAGRO-EQ</t>
+          <t>NSE:EMBDL-EQ</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>149</v>
+        <v>332</v>
       </c>
       <c r="F50" t="n">
-        <v>246.05</v>
+        <v>111.2</v>
       </c>
       <c r="G50" t="n">
-        <v>36661.45</v>
+        <v>36918.4</v>
       </c>
       <c r="H50" t="n">
-        <v>36.66145</v>
+        <v>36.91840000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>18.330725</v>
-      </c>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="n">
-        <v>-5188.042174999999</v>
-      </c>
-      <c r="L50" t="n">
-        <v>-12.28163992869875</v>
-      </c>
-      <c r="M50" t="n">
-        <v>280.5</v>
-      </c>
+        <v>18.4592</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.7400443722943723</v>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
         <v>49</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>45721</v>
+        <v>45729</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>NSE:LLOYDSME-EQ</t>
+          <t>NSE:BOMDYEING-EQ</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>34</v>
+        <v>288</v>
       </c>
       <c r="F51" t="n">
-        <v>1027.8</v>
+        <v>127.32</v>
       </c>
       <c r="G51" t="n">
-        <v>34945.2</v>
+        <v>36668.16</v>
       </c>
       <c r="H51" t="n">
-        <v>34.9452</v>
+        <v>36.66816</v>
       </c>
       <c r="I51" t="n">
-        <v>17.4726</v>
-      </c>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="n">
-        <v>-3321.517800000003</v>
-      </c>
-      <c r="L51" t="n">
-        <v>-8.554651007607108</v>
-      </c>
-      <c r="M51" t="n">
-        <v>1123.95</v>
-      </c>
+        <v>18.33408</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.7340634920634918</v>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
         <v>50</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>45722</v>
+        <v>45729</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NSE:63MOONS-EQ</t>
+          <t>NSE:TITAGARH-EQ</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2546,22 +2546,22 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F52" t="n">
-        <v>724.6</v>
+        <v>694.3</v>
       </c>
       <c r="G52" t="n">
-        <v>39128.4</v>
+        <v>36797.89999999999</v>
       </c>
       <c r="H52" t="n">
-        <v>39.1284</v>
+        <v>36.79789999999999</v>
       </c>
       <c r="I52" t="n">
-        <v>19.5642</v>
+        <v>18.39895</v>
       </c>
       <c r="J52" t="n">
-        <v>0.7836001524126019</v>
+        <v>0.7375595238095238</v>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
@@ -2572,54 +2572,50 @@
         <v>51</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>45722</v>
+        <v>45734</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>NSE:SARDAEN-EQ</t>
+          <t>NSE:CAMLINFINE-BE</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="F53" t="n">
-        <v>475.9</v>
+        <v>170.4</v>
       </c>
       <c r="G53" t="n">
-        <v>38547.9</v>
+        <v>38169.6</v>
       </c>
       <c r="H53" t="n">
-        <v>38.54790000000001</v>
+        <v>38.1696</v>
       </c>
       <c r="I53" t="n">
-        <v>19.27395</v>
-      </c>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="n">
-        <v>1128.828149999998</v>
-      </c>
-      <c r="L53" t="n">
-        <v>3.17615176151761</v>
-      </c>
-      <c r="M53" t="n">
-        <v>461.25</v>
-      </c>
+        <v>19.0848</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.7640959595959594</v>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
         <v>52</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>45723</v>
+        <v>45734</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>NSE:MCX-EQ</t>
+          <t>NSE:JBCHEPHARM-EQ</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2628,29 +2624,29 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="F54" t="n">
-        <v>4664.05</v>
+        <v>1590.3</v>
       </c>
       <c r="G54" t="n">
-        <v>27984.3</v>
+        <v>36576.9</v>
       </c>
       <c r="H54" t="n">
-        <v>27.9843</v>
+        <v>36.5769</v>
       </c>
       <c r="I54" t="n">
-        <v>13.99215</v>
+        <v>18.28845</v>
       </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="n">
-        <v>-5042.97645</v>
+        <v>-435.515349999999</v>
       </c>
       <c r="L54" t="n">
-        <v>-15.16129912415531</v>
+        <v>-1.029965460372776</v>
       </c>
       <c r="M54" t="n">
-        <v>5497.55</v>
+        <v>1606.85</v>
       </c>
     </row>
     <row r="55">
@@ -2658,132 +2654,136 @@
         <v>53</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>45723</v>
+        <v>45736</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>NSE:SAKSOFT-EQ</t>
+          <t>NSE:PARAGMILK-EQ</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>230</v>
+        <v>255</v>
       </c>
       <c r="F55" t="n">
-        <v>162.48</v>
+        <v>155.49</v>
       </c>
       <c r="G55" t="n">
-        <v>37370.39999999999</v>
+        <v>39649.95</v>
       </c>
       <c r="H55" t="n">
-        <v>37.3704</v>
+        <v>39.64995</v>
       </c>
       <c r="I55" t="n">
-        <v>18.6852</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0.7503528256120896</v>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
+        <v>19.824975</v>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="n">
+        <v>621.375075000004</v>
+      </c>
+      <c r="L55" t="n">
+        <v>1.747153513937977</v>
+      </c>
+      <c r="M55" t="n">
+        <v>152.82</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
         <v>54</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>45726</v>
+        <v>45740</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>NSE:INTELLECT-EQ</t>
+          <t>NSE:TITAGARH-EQ</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F56" t="n">
-        <v>653.7</v>
+        <v>820.9</v>
       </c>
       <c r="G56" t="n">
-        <v>41183.10000000001</v>
+        <v>43507.7</v>
       </c>
       <c r="H56" t="n">
-        <v>41.1831</v>
+        <v>43.5077</v>
       </c>
       <c r="I56" t="n">
-        <v>20.59155</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0.8281995305434432</v>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
+        <v>21.75385</v>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="n">
+        <v>6644.538450000007</v>
+      </c>
+      <c r="L56" t="n">
+        <v>18.23419271208414</v>
+      </c>
+      <c r="M56" t="n">
+        <v>694.2999999999998</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
         <v>55</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>45727</v>
+        <v>45741</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>NSE:FSL-EQ</t>
+          <t>NSE:NH-EQ</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>112</v>
+        <v>22</v>
       </c>
       <c r="F57" t="n">
-        <v>331.35</v>
+        <v>1647.2</v>
       </c>
       <c r="G57" t="n">
-        <v>37111.2</v>
+        <v>36238.4</v>
       </c>
       <c r="H57" t="n">
-        <v>37.1112</v>
+        <v>36.23840000000001</v>
       </c>
       <c r="I57" t="n">
-        <v>18.5556</v>
-      </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="n">
-        <v>-2598.066799999999</v>
-      </c>
-      <c r="L57" t="n">
-        <v>-6.411523796073998</v>
-      </c>
-      <c r="M57" t="n">
-        <v>354.05</v>
-      </c>
+        <v>18.1192</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.7394891774891776</v>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
         <v>56</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>45727</v>
+        <v>45741</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>NSE:SHAKTIPUMP-EQ</t>
+          <t>NSE:VIJAYA-EQ</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2792,22 +2792,22 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F58" t="n">
-        <v>888.3</v>
+        <v>1020.1</v>
       </c>
       <c r="G58" t="n">
-        <v>39085.2</v>
+        <v>36723.6</v>
       </c>
       <c r="H58" t="n">
-        <v>39.0852</v>
+        <v>36.7236</v>
       </c>
       <c r="I58" t="n">
-        <v>19.5426</v>
+        <v>18.3618</v>
       </c>
       <c r="J58" t="n">
-        <v>0.7969673466852061</v>
+        <v>0.7530238095238095</v>
       </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
@@ -2818,11 +2818,11 @@
         <v>57</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>45728</v>
+        <v>45742</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>NSE:63MOONS-EQ</t>
+          <t>NSE:AVALON-EQ</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2831,29 +2831,29 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F59" t="n">
-        <v>687</v>
+        <v>783.6</v>
       </c>
       <c r="G59" t="n">
-        <v>37098</v>
+        <v>44665.2</v>
       </c>
       <c r="H59" t="n">
-        <v>37.098</v>
+        <v>44.66520000000001</v>
       </c>
       <c r="I59" t="n">
-        <v>18.549</v>
+        <v>22.3326</v>
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="n">
-        <v>-2086.047000000001</v>
+        <v>5801.152200000002</v>
       </c>
       <c r="L59" t="n">
-        <v>-5.189069831631247</v>
+        <v>15.12524792477779</v>
       </c>
       <c r="M59" t="n">
-        <v>724.6</v>
+        <v>680.65</v>
       </c>
     </row>
     <row r="60">
@@ -2861,50 +2861,54 @@
         <v>58</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>45728</v>
+        <v>45742</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>NSE:SPARC-EQ</t>
+          <t>NSE:BEPL-EQ</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>307</v>
+        <v>355</v>
       </c>
       <c r="F60" t="n">
-        <v>124.48</v>
+        <v>107.92</v>
       </c>
       <c r="G60" t="n">
-        <v>38215.36</v>
+        <v>38311.6</v>
       </c>
       <c r="H60" t="n">
-        <v>38.21536</v>
+        <v>38.3116</v>
       </c>
       <c r="I60" t="n">
-        <v>19.10768</v>
-      </c>
-      <c r="J60" t="n">
-        <v>0.7645150168631309</v>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
+        <v>19.1558</v>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="n">
+        <v>1114.032600000004</v>
+      </c>
+      <c r="L60" t="n">
+        <v>3.154272605620351</v>
+      </c>
+      <c r="M60" t="n">
+        <v>104.62</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
         <v>59</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>45733</v>
+        <v>45743</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>NSE:FORTIS-EQ</t>
+          <t>NSE:JUBLFOOD-EQ</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2913,29 +2917,29 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F61" t="n">
-        <v>598.3</v>
+        <v>674.6</v>
       </c>
       <c r="G61" t="n">
-        <v>36496.3</v>
+        <v>41825.2</v>
       </c>
       <c r="H61" t="n">
-        <v>36.4963</v>
+        <v>41.8252</v>
       </c>
       <c r="I61" t="n">
-        <v>18.24815</v>
+        <v>20.9126</v>
       </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="n">
-        <v>-1338.794450000004</v>
+        <v>3976.562199999998</v>
       </c>
       <c r="L61" t="n">
-        <v>-3.398724469201593</v>
+        <v>10.68996636311428</v>
       </c>
       <c r="M61" t="n">
-        <v>619.35</v>
+        <v>609.45</v>
       </c>
     </row>
     <row r="62">
@@ -2943,11 +2947,11 @@
         <v>60</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>45733</v>
+        <v>45748</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>NSE:SPARC-EQ</t>
+          <t>NSE:CGCL-EQ</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2956,29 +2960,29 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>307</v>
+        <v>253</v>
       </c>
       <c r="F62" t="n">
-        <v>117.25</v>
+        <v>171.46</v>
       </c>
       <c r="G62" t="n">
-        <v>35995.75</v>
+        <v>43379.38</v>
       </c>
       <c r="H62" t="n">
-        <v>35.99575</v>
+        <v>43.37938</v>
       </c>
       <c r="I62" t="n">
-        <v>17.997875</v>
+        <v>21.68969</v>
       </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="n">
-        <v>-2273.603625000001</v>
+        <v>2932.980929999998</v>
       </c>
       <c r="L62" t="n">
-        <v>-5.80816195372751</v>
+        <v>7.424346845435746</v>
       </c>
       <c r="M62" t="n">
-        <v>124.48</v>
+        <v>159.61</v>
       </c>
     </row>
     <row r="63">
@@ -2986,128 +2990,140 @@
         <v>61</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>45734</v>
+        <v>45749</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>NSE:FORTIS-EQ</t>
+          <t>NSE:EMBDL-EQ</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>61</v>
+        <v>332</v>
       </c>
       <c r="F63" t="n">
-        <v>615.15</v>
+        <v>115.31</v>
       </c>
       <c r="G63" t="n">
-        <v>37524.15</v>
+        <v>38282.92</v>
       </c>
       <c r="H63" t="n">
-        <v>37.52415</v>
+        <v>38.28292</v>
       </c>
       <c r="I63" t="n">
-        <v>18.762075</v>
-      </c>
-      <c r="J63" t="n">
-        <v>0.7587123901038786</v>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
+        <v>19.14146</v>
+      </c>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="n">
+        <v>1307.09562</v>
+      </c>
+      <c r="L63" t="n">
+        <v>3.696043165467625</v>
+      </c>
+      <c r="M63" t="n">
+        <v>111.2</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
         <v>62</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>45734</v>
+        <v>45750</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>NSE:GOLDIAM-EQ</t>
+          <t>NSE:BOMDYEING-EQ</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>101</v>
+        <v>288</v>
       </c>
       <c r="F64" t="n">
-        <v>407.95</v>
+        <v>140.57</v>
       </c>
       <c r="G64" t="n">
-        <v>41202.95</v>
+        <v>40484.16</v>
       </c>
       <c r="H64" t="n">
-        <v>41.20295</v>
+        <v>40.48416</v>
       </c>
       <c r="I64" t="n">
-        <v>20.601475</v>
-      </c>
-      <c r="J64" t="n">
-        <v>0.8263916886839775</v>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
+        <v>20.24208</v>
+      </c>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="n">
+        <v>3755.27376</v>
+      </c>
+      <c r="L64" t="n">
+        <v>10.40684888469997</v>
+      </c>
+      <c r="M64" t="n">
+        <v>127.32</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
         <v>63</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>45734</v>
+        <v>45756</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>NSE:JAGSNPHARM-EQ</t>
+          <t>NSE:CAMLINFINE-BE</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>184</v>
+        <v>224</v>
       </c>
       <c r="F65" t="n">
-        <v>216.9</v>
+        <v>133.43</v>
       </c>
       <c r="G65" t="n">
-        <v>39909.6</v>
+        <v>29888.32</v>
       </c>
       <c r="H65" t="n">
-        <v>39.9096</v>
+        <v>29.88832</v>
       </c>
       <c r="I65" t="n">
-        <v>19.9548</v>
-      </c>
-      <c r="J65" t="n">
-        <v>0.7982195192045748</v>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
+        <v>14.94416</v>
+      </c>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="n">
+        <v>-8326.112479999998</v>
+      </c>
+      <c r="L65" t="n">
+        <v>-21.69600938967136</v>
+      </c>
+      <c r="M65" t="n">
+        <v>170.4</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
         <v>64</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>45734</v>
+        <v>45758</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>NSE:SAREGAMA-EQ</t>
+          <t>NSE:VIJAYA-EQ</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3116,29 +3132,29 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="F66" t="n">
-        <v>499.7</v>
+        <v>965.4</v>
       </c>
       <c r="G66" t="n">
-        <v>42474.5</v>
+        <v>34754.4</v>
       </c>
       <c r="H66" t="n">
-        <v>42.4745</v>
+        <v>34.7544</v>
       </c>
       <c r="I66" t="n">
-        <v>21.23725</v>
+        <v>17.3772</v>
       </c>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="n">
-        <v>153.038250000001</v>
+        <v>-2021.331599999997</v>
       </c>
       <c r="L66" t="n">
-        <v>0.5129236648898746</v>
+        <v>-5.362219390255851</v>
       </c>
       <c r="M66" t="n">
-        <v>497.15</v>
+        <v>1020.1</v>
       </c>
     </row>
     <row r="67">
@@ -3146,11 +3162,11 @@
         <v>65</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>45740</v>
+        <v>45762</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NSE:DEEPAKFERT-EQ</t>
+          <t>NSE:LTFOODS-EQ</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3159,22 +3175,22 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>35</v>
+        <v>101</v>
       </c>
       <c r="F67" t="n">
-        <v>1125.6</v>
+        <v>360.5</v>
       </c>
       <c r="G67" t="n">
-        <v>39396</v>
+        <v>36410.5</v>
       </c>
       <c r="H67" t="n">
-        <v>39.396</v>
+        <v>36.4105</v>
       </c>
       <c r="I67" t="n">
-        <v>19.698</v>
+        <v>18.20525</v>
       </c>
       <c r="J67" t="n">
-        <v>0.7934896550168409</v>
+        <v>0.7326071428571427</v>
       </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
@@ -3185,11 +3201,11 @@
         <v>66</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>45740</v>
+        <v>45762</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>NSE:EPACK-EQ</t>
+          <t>NSE:NH-EQ</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3198,29 +3214,29 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>109</v>
+        <v>22</v>
       </c>
       <c r="F68" t="n">
-        <v>356.85</v>
+        <v>1735.6</v>
       </c>
       <c r="G68" t="n">
-        <v>38896.65</v>
+        <v>38183.2</v>
       </c>
       <c r="H68" t="n">
-        <v>38.89665</v>
+        <v>38.1832</v>
       </c>
       <c r="I68" t="n">
-        <v>19.448325</v>
+        <v>19.0916</v>
       </c>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="n">
-        <v>-270.8949750000049</v>
+        <v>1887.525199999997</v>
       </c>
       <c r="L68" t="n">
-        <v>-0.5434782608695777</v>
+        <v>5.366682855755212</v>
       </c>
       <c r="M68" t="n">
-        <v>358.8000000000001</v>
+        <v>1647.2</v>
       </c>
     </row>
     <row r="69">
@@ -3228,54 +3244,50 @@
         <v>67</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>45740</v>
+        <v>45762</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>NSE:REFEX-EQ</t>
+          <t>NSE:RELINFRA-BE</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>102</v>
+        <v>146</v>
       </c>
       <c r="F69" t="n">
-        <v>396.35</v>
+        <v>255</v>
       </c>
       <c r="G69" t="n">
-        <v>40427.7</v>
+        <v>37230</v>
       </c>
       <c r="H69" t="n">
-        <v>40.42770000000001</v>
+        <v>37.23</v>
       </c>
       <c r="I69" t="n">
-        <v>20.21385</v>
-      </c>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="n">
-        <v>1637.658450000003</v>
-      </c>
-      <c r="L69" t="n">
-        <v>4.385040821701352</v>
-      </c>
-      <c r="M69" t="n">
-        <v>379.7</v>
-      </c>
+        <v>18.615</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.7464880952380952</v>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
         <v>68</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>45741</v>
+        <v>45768</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>NSE:BORORENEW-EQ</t>
+          <t>NSE:APOLLO-EQ</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3284,22 +3296,22 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>73</v>
+        <v>307</v>
       </c>
       <c r="F70" t="n">
-        <v>510.25</v>
+        <v>120.42</v>
       </c>
       <c r="G70" t="n">
-        <v>37248.25</v>
+        <v>36968.94</v>
       </c>
       <c r="H70" t="n">
-        <v>37.24825</v>
+        <v>36.96894</v>
       </c>
       <c r="I70" t="n">
-        <v>18.624125</v>
+        <v>18.48447</v>
       </c>
       <c r="J70" t="n">
-        <v>0.7540257500369036</v>
+        <v>0.7394047619047618</v>
       </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
@@ -3310,54 +3322,50 @@
         <v>69</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>45741</v>
+        <v>45770</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>NSE:PGEL-EQ</t>
+          <t>NSE:SPIC-EQ</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>47</v>
+        <v>451</v>
       </c>
       <c r="F71" t="n">
-        <v>883.75</v>
+        <v>83.41</v>
       </c>
       <c r="G71" t="n">
-        <v>41536.25</v>
+        <v>37617.91</v>
       </c>
       <c r="H71" t="n">
-        <v>41.53625</v>
+        <v>37.61790999999999</v>
       </c>
       <c r="I71" t="n">
-        <v>20.768125</v>
-      </c>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="n">
-        <v>4115.995624999994</v>
-      </c>
-      <c r="L71" t="n">
-        <v>11.18450022016731</v>
-      </c>
-      <c r="M71" t="n">
-        <v>794.8500000000001</v>
-      </c>
+        <v>18.808955</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.7535714285714286</v>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
         <v>70</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>45742</v>
+        <v>45771</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>NSE:AIIL-EQ</t>
+          <t>NSE:UNOMINDA-EQ</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3366,22 +3374,22 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="F72" t="n">
-        <v>1536</v>
+        <v>895.55</v>
       </c>
       <c r="G72" t="n">
-        <v>36864</v>
+        <v>36717.55</v>
       </c>
       <c r="H72" t="n">
-        <v>36.864</v>
+        <v>36.71755</v>
       </c>
       <c r="I72" t="n">
-        <v>18.432</v>
+        <v>18.358775</v>
       </c>
       <c r="J72" t="n">
-        <v>0.754789445669883</v>
+        <v>0.746436507936508</v>
       </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
@@ -3392,11 +3400,11 @@
         <v>71</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>45742</v>
+        <v>45772</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>NSE:GOLDIAM-EQ</t>
+          <t>NSE:APOLLO-EQ</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3405,29 +3413,29 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>101</v>
+        <v>307</v>
       </c>
       <c r="F73" t="n">
-        <v>386.55</v>
+        <v>111.74</v>
       </c>
       <c r="G73" t="n">
-        <v>39041.55</v>
+        <v>34304.18</v>
       </c>
       <c r="H73" t="n">
-        <v>39.04155</v>
+        <v>34.30418</v>
       </c>
       <c r="I73" t="n">
-        <v>19.520775</v>
+        <v>17.15209</v>
       </c>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="n">
-        <v>-2219.962324999998</v>
+        <v>-2716.216270000002</v>
       </c>
       <c r="L73" t="n">
-        <v>-5.245740899620046</v>
+        <v>-7.208104965952505</v>
       </c>
       <c r="M73" t="n">
-        <v>407.95</v>
+        <v>120.42</v>
       </c>
     </row>
     <row r="74">
@@ -3435,54 +3443,50 @@
         <v>72</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>45742</v>
+        <v>45776</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>NSE:SAKSOFT-EQ</t>
+          <t>NSE:DEEPAKFERT-EQ</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>230</v>
+        <v>29</v>
       </c>
       <c r="F74" t="n">
-        <v>150.95</v>
+        <v>1301.6</v>
       </c>
       <c r="G74" t="n">
-        <v>34718.5</v>
+        <v>37746.39999999999</v>
       </c>
       <c r="H74" t="n">
-        <v>34.7185</v>
+        <v>37.74639999999999</v>
       </c>
       <c r="I74" t="n">
-        <v>17.35925</v>
-      </c>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="n">
-        <v>-2703.977749999994</v>
-      </c>
-      <c r="L74" t="n">
-        <v>-7.096258000984721</v>
-      </c>
-      <c r="M74" t="n">
-        <v>162.48</v>
-      </c>
+        <v>18.8732</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.761277417027417</v>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
         <v>73</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>45748</v>
+        <v>45779</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>NSE:INTELLECT-EQ</t>
+          <t>NSE:LTFOODS-EQ</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3491,29 +3495,29 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="F75" t="n">
-        <v>684.25</v>
+        <v>341.55</v>
       </c>
       <c r="G75" t="n">
-        <v>43107.75</v>
+        <v>34496.55</v>
       </c>
       <c r="H75" t="n">
-        <v>43.10775</v>
+        <v>34.49655000000001</v>
       </c>
       <c r="I75" t="n">
-        <v>21.553875</v>
+        <v>17.248275</v>
       </c>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="n">
-        <v>1859.988374999997</v>
+        <v>-1965.694824999999</v>
       </c>
       <c r="L75" t="n">
-        <v>4.673397582989131</v>
+        <v>-5.256588072122049</v>
       </c>
       <c r="M75" t="n">
-        <v>653.7</v>
+        <v>360.5</v>
       </c>
     </row>
     <row r="76">
@@ -3521,11 +3525,11 @@
         <v>74</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>45748</v>
+        <v>45779</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>NSE:SHAKTIPUMP-EQ</t>
+          <t>NSE:SPIC-EQ</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3534,29 +3538,29 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>44</v>
+        <v>451</v>
       </c>
       <c r="F76" t="n">
-        <v>956.45</v>
+        <v>78.87</v>
       </c>
       <c r="G76" t="n">
-        <v>42083.8</v>
+        <v>35570.37</v>
       </c>
       <c r="H76" t="n">
-        <v>42.0838</v>
+        <v>35.57037</v>
       </c>
       <c r="I76" t="n">
-        <v>21.0419</v>
+        <v>17.785185</v>
       </c>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="n">
-        <v>2935.474300000004</v>
+        <v>-2100.895554999996</v>
       </c>
       <c r="L76" t="n">
-        <v>7.671957671957682</v>
+        <v>-5.442992446948798</v>
       </c>
       <c r="M76" t="n">
-        <v>888.3</v>
+        <v>83.41</v>
       </c>
     </row>
     <row r="77">
@@ -3564,11 +3568,11 @@
         <v>75</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>45754</v>
+        <v>45783</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>NSE:JAGSNPHARM-EQ</t>
+          <t>NSE:RELINFRA-BE</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3577,29 +3581,29 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>184</v>
+        <v>146</v>
       </c>
       <c r="F77" t="n">
-        <v>202.88</v>
+        <v>236.35</v>
       </c>
       <c r="G77" t="n">
-        <v>37329.92</v>
+        <v>34507.1</v>
       </c>
       <c r="H77" t="n">
-        <v>37.32992</v>
+        <v>34.5071</v>
       </c>
       <c r="I77" t="n">
-        <v>18.66496</v>
+        <v>17.25355</v>
       </c>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="n">
-        <v>-2635.674880000002</v>
+        <v>-2774.660650000001</v>
       </c>
       <c r="L77" t="n">
-        <v>-6.4638082065468</v>
+        <v>-7.313725490196081</v>
       </c>
       <c r="M77" t="n">
-        <v>216.9</v>
+        <v>255</v>
       </c>
     </row>
     <row r="78">
@@ -3607,54 +3611,50 @@
         <v>76</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>45755</v>
+        <v>45790</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>NSE:FORTIS-EQ</t>
+          <t>NSE:SAPPHIRE-EQ</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>61</v>
+        <v>126</v>
       </c>
       <c r="F78" t="n">
-        <v>648.85</v>
+        <v>304.2</v>
       </c>
       <c r="G78" t="n">
-        <v>39579.85</v>
+        <v>38329.2</v>
       </c>
       <c r="H78" t="n">
-        <v>39.57985</v>
+        <v>38.3292</v>
       </c>
       <c r="I78" t="n">
-        <v>19.789925</v>
-      </c>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="n">
-        <v>1996.330225000002</v>
-      </c>
-      <c r="L78" t="n">
-        <v>5.478338616597585</v>
-      </c>
-      <c r="M78" t="n">
-        <v>615.15</v>
-      </c>
+        <v>19.1646</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.7677103174603174</v>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
         <v>77</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>45755</v>
+        <v>45793</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>NSE:MANKIND-EQ</t>
+          <t>NSE:PAYTM-EQ</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3663,22 +3663,22 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="F79" t="n">
-        <v>2347.5</v>
+        <v>852.35</v>
       </c>
       <c r="G79" t="n">
-        <v>37560</v>
+        <v>38355.75</v>
       </c>
       <c r="H79" t="n">
-        <v>37.56</v>
+        <v>38.35575</v>
       </c>
       <c r="I79" t="n">
-        <v>18.78</v>
+        <v>19.177875</v>
       </c>
       <c r="J79" t="n">
-        <v>0.7639815944696484</v>
+        <v>0.7757777777777776</v>
       </c>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
@@ -3689,11 +3689,11 @@
         <v>78</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>45756</v>
+        <v>45797</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>NSE:BORORENEW-EQ</t>
+          <t>NSE:DEEPAKFERT-EQ</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3702,29 +3702,29 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="F80" t="n">
-        <v>462</v>
+        <v>1374.2</v>
       </c>
       <c r="G80" t="n">
-        <v>33726</v>
+        <v>39851.8</v>
       </c>
       <c r="H80" t="n">
-        <v>33.726</v>
+        <v>39.8518</v>
       </c>
       <c r="I80" t="n">
-        <v>16.863</v>
+        <v>19.9259</v>
       </c>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="n">
-        <v>-3572.839</v>
+        <v>2045.622300000004</v>
       </c>
       <c r="L80" t="n">
-        <v>-9.456148946594807</v>
+        <v>5.577750460971123</v>
       </c>
       <c r="M80" t="n">
-        <v>510.25</v>
+        <v>1301.6</v>
       </c>
     </row>
     <row r="81">
@@ -3732,50 +3732,54 @@
         <v>79</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>45762</v>
+        <v>45804</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>NSE:SKYGOLD-EQ</t>
+          <t>NSE:UNOMINDA-EQ</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>112</v>
+        <v>41</v>
       </c>
       <c r="F81" t="n">
-        <v>335.9</v>
+        <v>1010.35</v>
       </c>
       <c r="G81" t="n">
-        <v>37620.8</v>
+        <v>41424.35</v>
       </c>
       <c r="H81" t="n">
-        <v>37.6208</v>
+        <v>41.42435</v>
       </c>
       <c r="I81" t="n">
-        <v>18.8104</v>
-      </c>
-      <c r="J81" t="n">
-        <v>0.7545608893556279</v>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
+        <v>20.712175</v>
+      </c>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="n">
+        <v>4644.663475000008</v>
+      </c>
+      <c r="L81" t="n">
+        <v>12.81893808274247</v>
+      </c>
+      <c r="M81" t="n">
+        <v>895.5499999999998</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
         <v>80</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>45762</v>
+        <v>45806</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>NSE:WOCKPHARMA-EQ</t>
+          <t>NSE:ACUTAAS-EQ</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3784,22 +3788,22 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F82" t="n">
-        <v>1402.3</v>
+        <v>1179.9</v>
       </c>
       <c r="G82" t="n">
-        <v>37862.1</v>
+        <v>37756.8</v>
       </c>
       <c r="H82" t="n">
-        <v>37.8621</v>
+        <v>37.75680000000001</v>
       </c>
       <c r="I82" t="n">
-        <v>18.93105</v>
+        <v>18.8784</v>
       </c>
       <c r="J82" t="n">
-        <v>0.7718362544996228</v>
+        <v>0.7570476190476191</v>
       </c>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
@@ -3810,54 +3814,50 @@
         <v>81</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>45763</v>
+        <v>45807</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>NSE:AIIL-EQ</t>
+          <t>NSE:POLICYBZR-EQ</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F83" t="n">
-        <v>1722.4</v>
+        <v>1761.6</v>
       </c>
       <c r="G83" t="n">
-        <v>41337.60000000001</v>
+        <v>36993.6</v>
       </c>
       <c r="H83" t="n">
-        <v>41.33760000000001</v>
+        <v>36.9936</v>
       </c>
       <c r="I83" t="n">
-        <v>20.6688</v>
-      </c>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="n">
-        <v>4411.593600000002</v>
-      </c>
-      <c r="L83" t="n">
-        <v>12.13541666666667</v>
-      </c>
-      <c r="M83" t="n">
-        <v>1536</v>
-      </c>
+        <v>18.4968</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0.7527857142857141</v>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
         <v>82</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>45763</v>
+        <v>45811</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>NSE:WEL-EQ</t>
+          <t>NSE:HEG-EQ</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3866,22 +3866,22 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>229</v>
+        <v>72</v>
       </c>
       <c r="F84" t="n">
-        <v>173.55</v>
+        <v>517.35</v>
       </c>
       <c r="G84" t="n">
-        <v>39742.95</v>
+        <v>37249.2</v>
       </c>
       <c r="H84" t="n">
-        <v>39.74295000000001</v>
+        <v>37.2492</v>
       </c>
       <c r="I84" t="n">
-        <v>19.871475</v>
+        <v>18.6246</v>
       </c>
       <c r="J84" t="n">
-        <v>0.7965974475135575</v>
+        <v>0.7503340548340547</v>
       </c>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
@@ -3892,93 +3892,93 @@
         <v>83</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>45770</v>
+        <v>45811</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>NSE:DEEPAKFERT-EQ</t>
+          <t>NSE:MONARCH-EQ</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>35</v>
+        <v>131</v>
       </c>
       <c r="F85" t="n">
-        <v>1283.4</v>
+        <v>305.45</v>
       </c>
       <c r="G85" t="n">
-        <v>44919</v>
+        <v>40013.95</v>
       </c>
       <c r="H85" t="n">
-        <v>44.919</v>
+        <v>40.01395</v>
       </c>
       <c r="I85" t="n">
-        <v>22.4595</v>
-      </c>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="n">
-        <v>5455.621500000007</v>
-      </c>
-      <c r="L85" t="n">
-        <v>14.01918976545844</v>
-      </c>
-      <c r="M85" t="n">
-        <v>1125.6</v>
-      </c>
+        <v>20.006975</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0.8048928571428573</v>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
         <v>84</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>45770</v>
+        <v>45811</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>NSE:MAFANG-EQ</t>
+          <t>NSE:SAPPHIRE-EQ</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>377</v>
+        <v>126</v>
       </c>
       <c r="F86" t="n">
-        <v>109.29</v>
+        <v>310.65</v>
       </c>
       <c r="G86" t="n">
-        <v>41202.33</v>
+        <v>39141.89999999999</v>
       </c>
       <c r="H86" t="n">
-        <v>41.20233</v>
+        <v>39.14189999999999</v>
       </c>
       <c r="I86" t="n">
-        <v>20.601165</v>
-      </c>
-      <c r="J86" t="n">
-        <v>0.8249325044671653</v>
-      </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
+        <v>19.57095</v>
+      </c>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="n">
+        <v>753.9871499999986</v>
+      </c>
+      <c r="L86" t="n">
+        <v>2.12031558185404</v>
+      </c>
+      <c r="M86" t="n">
+        <v>304.2</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
         <v>85</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>45772</v>
+        <v>45814</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>NSE:RELAXO-EQ</t>
+          <t>NSE:INDRAMEDCO-EQ</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3987,22 +3987,22 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F87" t="n">
-        <v>423.25</v>
+        <v>430.1</v>
       </c>
       <c r="G87" t="n">
-        <v>37669.25</v>
+        <v>38709</v>
       </c>
       <c r="H87" t="n">
-        <v>37.66925</v>
+        <v>38.709</v>
       </c>
       <c r="I87" t="n">
-        <v>18.834625</v>
+        <v>19.3545</v>
       </c>
       <c r="J87" t="n">
-        <v>0.7607748829825218</v>
+        <v>0.7780050505050505</v>
       </c>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
@@ -4013,11 +4013,11 @@
         <v>86</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>45772</v>
+        <v>45817</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>NSE:SKYGOLD-EQ</t>
+          <t>NSE:ACUTAAS-EQ</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4026,29 +4026,29 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="F88" t="n">
-        <v>315.3</v>
+        <v>1118</v>
       </c>
       <c r="G88" t="n">
-        <v>35313.6</v>
+        <v>35776</v>
       </c>
       <c r="H88" t="n">
-        <v>35.3136</v>
+        <v>35.776</v>
       </c>
       <c r="I88" t="n">
-        <v>17.6568</v>
+        <v>17.888</v>
       </c>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="n">
-        <v>-2360.170399999996</v>
+        <v>-2034.464000000003</v>
       </c>
       <c r="L88" t="n">
-        <v>-6.132777612384629</v>
+        <v>-5.24620730570388</v>
       </c>
       <c r="M88" t="n">
-        <v>335.9</v>
+        <v>1179.9</v>
       </c>
     </row>
     <row r="89">
@@ -4056,132 +4056,136 @@
         <v>87</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>45775</v>
+        <v>45819</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>NSE:WEL-EQ</t>
+          <t>NSE:PARADEEP-EQ</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>229</v>
+        <v>210</v>
       </c>
       <c r="F89" t="n">
-        <v>161.7</v>
+        <v>175.12</v>
       </c>
       <c r="G89" t="n">
-        <v>37029.3</v>
+        <v>36775.2</v>
       </c>
       <c r="H89" t="n">
-        <v>37.0293</v>
+        <v>36.77520000000001</v>
       </c>
       <c r="I89" t="n">
-        <v>18.51465</v>
-      </c>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="n">
-        <v>-2769.193950000005</v>
-      </c>
-      <c r="L89" t="n">
-        <v>-6.828003457216952</v>
-      </c>
-      <c r="M89" t="n">
-        <v>173.55</v>
-      </c>
+        <v>18.3876</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0.7377380952380953</v>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
         <v>88</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>45776</v>
+        <v>45820</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>NSE:ACUTAAS-EQ</t>
+          <t>NSE:PAYTM-EQ</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F90" t="n">
-        <v>1090.3</v>
+        <v>895.4</v>
       </c>
       <c r="G90" t="n">
-        <v>38160.5</v>
+        <v>40293</v>
       </c>
       <c r="H90" t="n">
-        <v>38.1605</v>
+        <v>40.293</v>
       </c>
       <c r="I90" t="n">
-        <v>19.08025</v>
-      </c>
-      <c r="J90" t="n">
-        <v>0.7743524533139947</v>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
+        <v>20.1465</v>
+      </c>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="n">
+        <v>1876.810499999998</v>
+      </c>
+      <c r="L90" t="n">
+        <v>5.050742066052672</v>
+      </c>
+      <c r="M90" t="n">
+        <v>852.35</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
         <v>89</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>45776</v>
+        <v>45826</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>NSE:AVANTIFEED-EQ</t>
+          <t>NSE:INDRAMEDCO-EQ</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="F91" t="n">
-        <v>890.4</v>
+        <v>399.35</v>
       </c>
       <c r="G91" t="n">
-        <v>37396.8</v>
+        <v>35941.5</v>
       </c>
       <c r="H91" t="n">
-        <v>37.3968</v>
+        <v>35.9415</v>
       </c>
       <c r="I91" t="n">
-        <v>18.6984</v>
-      </c>
-      <c r="J91" t="n">
-        <v>0.7522295691660819</v>
-      </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
+        <v>17.97075</v>
+      </c>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="n">
+        <v>-2821.41225</v>
+      </c>
+      <c r="L91" t="n">
+        <v>-7.149500116252034</v>
+      </c>
+      <c r="M91" t="n">
+        <v>430.1</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
         <v>90</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>45776</v>
+        <v>45826</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>NSE:MANKIND-EQ</t>
+          <t>NSE:PARADEEP-EQ</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4190,29 +4194,29 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>16</v>
+        <v>210</v>
       </c>
       <c r="F92" t="n">
-        <v>2556.9</v>
+        <v>165.83</v>
       </c>
       <c r="G92" t="n">
-        <v>40910.4</v>
+        <v>34824.3</v>
       </c>
       <c r="H92" t="n">
-        <v>40.9104</v>
+        <v>34.8243</v>
       </c>
       <c r="I92" t="n">
-        <v>20.4552</v>
+        <v>17.41215</v>
       </c>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="n">
-        <v>3289.034400000001</v>
+        <v>-2003.136450000004</v>
       </c>
       <c r="L92" t="n">
-        <v>8.920127795527161</v>
+        <v>-5.30493375970764</v>
       </c>
       <c r="M92" t="n">
-        <v>2347.5</v>
+        <v>175.12</v>
       </c>
     </row>
     <row r="93">
@@ -4220,11 +4224,11 @@
         <v>91</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>45776</v>
+        <v>45826</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>NSE:MUTHOOTFIN-EQ</t>
+          <t>NSE:YATHARTH-EQ</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4233,22 +4237,22 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="F93" t="n">
-        <v>2152.3</v>
+        <v>517.3</v>
       </c>
       <c r="G93" t="n">
-        <v>36589.10000000001</v>
+        <v>39314.8</v>
       </c>
       <c r="H93" t="n">
-        <v>36.58910000000001</v>
+        <v>39.3148</v>
       </c>
       <c r="I93" t="n">
-        <v>18.29455</v>
+        <v>19.6574</v>
       </c>
       <c r="J93" t="n">
-        <v>0.7505310848171011</v>
+        <v>0.7924523809523809</v>
       </c>
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr"/>
@@ -4259,11 +4263,11 @@
         <v>92</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>45776</v>
+        <v>45827</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>NSE:WEL-EQ</t>
+          <t>NSE:LTF-EQ</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4272,22 +4276,22 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>238</v>
+        <v>206</v>
       </c>
       <c r="F94" t="n">
-        <v>157.78</v>
+        <v>187.51</v>
       </c>
       <c r="G94" t="n">
-        <v>37551.64</v>
+        <v>38627.06</v>
       </c>
       <c r="H94" t="n">
-        <v>37.55164</v>
+        <v>38.62706</v>
       </c>
       <c r="I94" t="n">
-        <v>18.77582</v>
+        <v>19.31353</v>
       </c>
       <c r="J94" t="n">
-        <v>0.7525187255947066</v>
+        <v>0.7760952380952381</v>
       </c>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
@@ -4298,50 +4302,54 @@
         <v>93</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>45777</v>
+        <v>45828</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>NSE:RELINFRA-BE</t>
+          <t>NSE:POLICYBZR-EQ</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>148</v>
+        <v>21</v>
       </c>
       <c r="F95" t="n">
-        <v>254.55</v>
+        <v>1901.3</v>
       </c>
       <c r="G95" t="n">
-        <v>37673.4</v>
+        <v>39927.3</v>
       </c>
       <c r="H95" t="n">
-        <v>37.6734</v>
+        <v>39.9273</v>
       </c>
       <c r="I95" t="n">
-        <v>18.8367</v>
-      </c>
-      <c r="J95" t="n">
-        <v>0.7558974155310376</v>
-      </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
+        <v>19.96365</v>
+      </c>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="n">
+        <v>2873.809050000001</v>
+      </c>
+      <c r="L95" t="n">
+        <v>7.930290644868304</v>
+      </c>
+      <c r="M95" t="n">
+        <v>1761.6</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
         <v>94</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>45777</v>
+        <v>45832</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>NSE:WOCKPHARMA-EQ</t>
+          <t>NSE:HEG-EQ</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4350,29 +4358,29 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="F96" t="n">
-        <v>1296.7</v>
+        <v>491.4</v>
       </c>
       <c r="G96" t="n">
-        <v>35010.9</v>
+        <v>35380.8</v>
       </c>
       <c r="H96" t="n">
-        <v>35.0109</v>
+        <v>35.38079999999999</v>
       </c>
       <c r="I96" t="n">
-        <v>17.50545</v>
+        <v>17.6904</v>
       </c>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="n">
-        <v>-2903.716349999997</v>
+        <v>-1921.471200000003</v>
       </c>
       <c r="L96" t="n">
-        <v>-7.530485630749477</v>
+        <v>-5.015946651203256</v>
       </c>
       <c r="M96" t="n">
-        <v>1402.3</v>
+        <v>517.35</v>
       </c>
     </row>
     <row r="97">
@@ -4380,11 +4388,11 @@
         <v>95</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>45783</v>
+        <v>45832</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>NSE:RELINFRA-BE</t>
+          <t>NSE:MONARCH-EQ</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4393,29 +4401,29 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="F97" t="n">
-        <v>236.35</v>
+        <v>317.6</v>
       </c>
       <c r="G97" t="n">
-        <v>34979.8</v>
+        <v>41605.60000000001</v>
       </c>
       <c r="H97" t="n">
-        <v>34.9798</v>
+        <v>41.60560000000001</v>
       </c>
       <c r="I97" t="n">
-        <v>17.4899</v>
+        <v>20.8028</v>
       </c>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="n">
-        <v>-2746.069700000003</v>
+        <v>1529.241600000004</v>
       </c>
       <c r="L97" t="n">
-        <v>-7.149872323708512</v>
+        <v>3.977737763954832</v>
       </c>
       <c r="M97" t="n">
-        <v>254.55</v>
+        <v>305.45</v>
       </c>
     </row>
     <row r="98">
@@ -4423,11 +4431,11 @@
         <v>96</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>45785</v>
+        <v>45839</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>NSE:WOCKPHARMA-EQ</t>
+          <t>NSE:PARAGMILK-EQ</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4436,22 +4444,22 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>31</v>
+        <v>171</v>
       </c>
       <c r="F98" t="n">
-        <v>1235.2</v>
+        <v>224.6</v>
       </c>
       <c r="G98" t="n">
-        <v>38291.2</v>
+        <v>38406.6</v>
       </c>
       <c r="H98" t="n">
-        <v>38.2912</v>
+        <v>38.4066</v>
       </c>
       <c r="I98" t="n">
-        <v>19.1456</v>
+        <v>19.2033</v>
       </c>
       <c r="J98" t="n">
-        <v>0.7670350574139602</v>
+        <v>0.7717857142857142</v>
       </c>
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr"/>
@@ -4462,50 +4470,46 @@
         <v>97</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>45786</v>
+        <v>45840</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>NSE:RELAXO-EQ</t>
+          <t>NSE:EPL-EQ</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>89</v>
+        <v>162</v>
       </c>
       <c r="F99" t="n">
-        <v>401.85</v>
+        <v>240.52</v>
       </c>
       <c r="G99" t="n">
-        <v>35764.65</v>
+        <v>38964.24000000001</v>
       </c>
       <c r="H99" t="n">
-        <v>35.76465</v>
+        <v>38.96424</v>
       </c>
       <c r="I99" t="n">
-        <v>17.882325</v>
-      </c>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="n">
-        <v>-1958.246974999998</v>
-      </c>
-      <c r="L99" t="n">
-        <v>-5.056113408151205</v>
-      </c>
-      <c r="M99" t="n">
-        <v>423.25</v>
-      </c>
+        <v>19.48212</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0.7813928571428574</v>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
         <v>98</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>45790</v>
+        <v>45842</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -4518,22 +4522,22 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="F100" t="n">
-        <v>707.6</v>
+        <v>1019.6</v>
       </c>
       <c r="G100" t="n">
-        <v>37502.8</v>
+        <v>36705.6</v>
       </c>
       <c r="H100" t="n">
-        <v>37.5028</v>
+        <v>36.7056</v>
       </c>
       <c r="I100" t="n">
-        <v>18.7514</v>
+        <v>18.3528</v>
       </c>
       <c r="J100" t="n">
-        <v>0.7640421972115908</v>
+        <v>0.7485476190476191</v>
       </c>
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
@@ -4544,11 +4548,11 @@
         <v>99</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>45790</v>
+        <v>45846</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>NSE:BLUEJET-EQ</t>
+          <t>NSE:WELCORP-EQ</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4557,22 +4561,22 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="F101" t="n">
-        <v>769</v>
+        <v>914.9</v>
       </c>
       <c r="G101" t="n">
-        <v>37681</v>
+        <v>37510.9</v>
       </c>
       <c r="H101" t="n">
-        <v>37.681</v>
+        <v>37.5109</v>
       </c>
       <c r="I101" t="n">
-        <v>18.8405</v>
+        <v>18.75545</v>
       </c>
       <c r="J101" t="n">
-        <v>0.7585018662270272</v>
+        <v>0.7628095238095237</v>
       </c>
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr"/>
@@ -4583,50 +4587,54 @@
         <v>100</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>45792</v>
+        <v>45848</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>NSE:SHAKTIPUMP-EQ</t>
+          <t>NSE:LTF-EQ</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>43</v>
+        <v>206</v>
       </c>
       <c r="F102" t="n">
-        <v>852.75</v>
+        <v>206.77</v>
       </c>
       <c r="G102" t="n">
-        <v>36668.25</v>
+        <v>42594.62</v>
       </c>
       <c r="H102" t="n">
-        <v>36.66825</v>
+        <v>42.59462000000001</v>
       </c>
       <c r="I102" t="n">
-        <v>18.334125</v>
-      </c>
-      <c r="J102" t="n">
-        <v>0.750386672499963</v>
-      </c>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr"/>
+        <v>21.29731</v>
+      </c>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="n">
+        <v>3903.668070000004</v>
+      </c>
+      <c r="L102" t="n">
+        <v>10.27145218921659</v>
+      </c>
+      <c r="M102" t="n">
+        <v>187.51</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
         <v>101</v>
       </c>
       <c r="B103" s="2" t="n">
-        <v>45797</v>
+        <v>45848</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>NSE:ACUTAAS-EQ</t>
+          <t>NSE:YATHARTH-EQ</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -4635,29 +4643,29 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="F103" t="n">
-        <v>1178.5</v>
+        <v>621.6</v>
       </c>
       <c r="G103" t="n">
-        <v>41247.5</v>
+        <v>47241.6</v>
       </c>
       <c r="H103" t="n">
-        <v>41.2475</v>
+        <v>47.2416</v>
       </c>
       <c r="I103" t="n">
-        <v>20.62375</v>
+        <v>23.6208</v>
       </c>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="n">
-        <v>3025.128750000002</v>
+        <v>7855.937600000005</v>
       </c>
       <c r="L103" t="n">
-        <v>8.089516646794465</v>
+        <v>20.16238159675238</v>
       </c>
       <c r="M103" t="n">
-        <v>1090.3</v>
+        <v>517.3</v>
       </c>
     </row>
     <row r="104">
@@ -4665,97 +4673,89 @@
         <v>102</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>45797</v>
+        <v>45854</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>NSE:AVANTIFEED-EQ</t>
+          <t>NSE:HUBTOWN-EQ</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>42</v>
+        <v>125</v>
       </c>
       <c r="F104" t="n">
-        <v>870.05</v>
+        <v>292.85</v>
       </c>
       <c r="G104" t="n">
-        <v>36542.1</v>
+        <v>36606.25</v>
       </c>
       <c r="H104" t="n">
-        <v>36.5421</v>
+        <v>36.60625</v>
       </c>
       <c r="I104" t="n">
-        <v>18.27105</v>
-      </c>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="n">
-        <v>-909.5131499999961</v>
-      </c>
-      <c r="L104" t="n">
-        <v>-2.28548966756513</v>
-      </c>
-      <c r="M104" t="n">
-        <v>890.3999999999999</v>
-      </c>
+        <v>18.303125</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0.7330833333333334</v>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
         <v>103</v>
       </c>
       <c r="B105" s="2" t="n">
-        <v>45797</v>
+        <v>45855</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>NSE:WEL-EQ</t>
+          <t>NSE:CUB-EQ</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>238</v>
+        <v>184</v>
       </c>
       <c r="F105" t="n">
-        <v>172.15</v>
+        <v>216.45</v>
       </c>
       <c r="G105" t="n">
-        <v>40971.7</v>
+        <v>39826.8</v>
       </c>
       <c r="H105" t="n">
-        <v>40.97170000000001</v>
+        <v>39.8268</v>
       </c>
       <c r="I105" t="n">
-        <v>20.48585</v>
-      </c>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="n">
-        <v>3358.602450000001</v>
-      </c>
-      <c r="L105" t="n">
-        <v>9.107618202560531</v>
-      </c>
-      <c r="M105" t="n">
-        <v>157.78</v>
-      </c>
+        <v>19.9134</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0.7980238095238096</v>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
         <v>104</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>45798</v>
+        <v>45860</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>NSE:MUTHOOTFIN-EQ</t>
+          <t>NSE:PARAGMILK-EQ</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -4764,29 +4764,29 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>17</v>
+        <v>171</v>
       </c>
       <c r="F106" t="n">
-        <v>2089.6</v>
+        <v>243.1</v>
       </c>
       <c r="G106" t="n">
-        <v>35523.2</v>
+        <v>41570.1</v>
       </c>
       <c r="H106" t="n">
-        <v>35.5232</v>
+        <v>41.5701</v>
       </c>
       <c r="I106" t="n">
-        <v>17.7616</v>
+        <v>20.78505</v>
       </c>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="n">
-        <v>-1119.184800000005</v>
+        <v>3101.14485</v>
       </c>
       <c r="L106" t="n">
-        <v>-2.913162663197522</v>
+        <v>8.236865538735531</v>
       </c>
       <c r="M106" t="n">
-        <v>2152.3</v>
+        <v>224.6</v>
       </c>
     </row>
     <row r="107">
@@ -4794,11 +4794,11 @@
         <v>105</v>
       </c>
       <c r="B107" s="2" t="n">
-        <v>45800</v>
+        <v>45861</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>NSE:MAFANG-EQ</t>
+          <t>NSE:EPL-EQ</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -4807,29 +4807,29 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>377</v>
+        <v>162</v>
       </c>
       <c r="F107" t="n">
-        <v>136.31</v>
+        <v>232.43</v>
       </c>
       <c r="G107" t="n">
-        <v>51388.87</v>
+        <v>37653.66</v>
       </c>
       <c r="H107" t="n">
-        <v>51.38887</v>
+        <v>37.65366</v>
       </c>
       <c r="I107" t="n">
-        <v>25.694435</v>
+        <v>18.82683</v>
       </c>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="n">
-        <v>10109.456695</v>
+        <v>-1367.060490000005</v>
       </c>
       <c r="L107" t="n">
-        <v>24.72321346875286</v>
+        <v>-3.363545651089319</v>
       </c>
       <c r="M107" t="n">
-        <v>109.29</v>
+        <v>240.52</v>
       </c>
     </row>
     <row r="108">
@@ -4837,7 +4837,7 @@
         <v>106</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>45803</v>
+        <v>45863</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -4850,29 +4850,29 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="F108" t="n">
-        <v>820.7</v>
+        <v>1043.2</v>
       </c>
       <c r="G108" t="n">
-        <v>43497.10000000001</v>
+        <v>37555.2</v>
       </c>
       <c r="H108" t="n">
-        <v>43.4971</v>
+        <v>37.55520000000001</v>
       </c>
       <c r="I108" t="n">
-        <v>21.74855</v>
+        <v>18.7776</v>
       </c>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="n">
-        <v>5929.054350000001</v>
+        <v>793.2672000000049</v>
       </c>
       <c r="L108" t="n">
-        <v>15.98360655737705</v>
+        <v>2.314633189486087</v>
       </c>
       <c r="M108" t="n">
-        <v>707.6</v>
+        <v>1019.6</v>
       </c>
     </row>
     <row r="109">
@@ -4880,136 +4880,132 @@
         <v>107</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>45806</v>
+        <v>45866</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>NSE:WOCKPHARMA-EQ</t>
+          <t>NSE:PARAGMILK-EQ</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>31</v>
+        <v>164</v>
       </c>
       <c r="F109" t="n">
-        <v>1346.8</v>
+        <v>248.22</v>
       </c>
       <c r="G109" t="n">
-        <v>41750.8</v>
+        <v>40708.08</v>
       </c>
       <c r="H109" t="n">
-        <v>41.7508</v>
+        <v>40.70808</v>
       </c>
       <c r="I109" t="n">
-        <v>20.8754</v>
-      </c>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="n">
-        <v>3396.973799999997</v>
-      </c>
-      <c r="L109" t="n">
-        <v>9.034974093264241</v>
-      </c>
-      <c r="M109" t="n">
-        <v>1235.2</v>
-      </c>
+        <v>20.35404</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0.8148214285714285</v>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
         <v>108</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>45811</v>
+        <v>45867</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>NSE:AMBER-EQ</t>
+          <t>NSE:WELCORP-EQ</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="F110" t="n">
-        <v>6327.5</v>
+        <v>924.55</v>
       </c>
       <c r="G110" t="n">
-        <v>37965</v>
+        <v>37906.55</v>
       </c>
       <c r="H110" t="n">
-        <v>37.965</v>
+        <v>37.90655</v>
       </c>
       <c r="I110" t="n">
-        <v>18.9825</v>
-      </c>
-      <c r="J110" t="n">
-        <v>0.7761156543073413</v>
-      </c>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr"/>
+        <v>18.953275</v>
+      </c>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="n">
+        <v>338.7901749999944</v>
+      </c>
+      <c r="L110" t="n">
+        <v>1.054760083069173</v>
+      </c>
+      <c r="M110" t="n">
+        <v>914.9000000000001</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
         <v>109</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>45813</v>
+        <v>45870</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>NSE:BLUEJET-EQ</t>
+          <t>NSE:NAM-INDIA-EQ</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E111" t="n">
         <v>49</v>
       </c>
       <c r="F111" t="n">
-        <v>923.65</v>
+        <v>803.8</v>
       </c>
       <c r="G111" t="n">
-        <v>45258.85</v>
+        <v>39386.2</v>
       </c>
       <c r="H111" t="n">
-        <v>45.25885</v>
+        <v>39.3862</v>
       </c>
       <c r="I111" t="n">
-        <v>22.629425</v>
-      </c>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="n">
-        <v>7509.961724999998</v>
-      </c>
-      <c r="L111" t="n">
-        <v>20.11053315994798</v>
-      </c>
-      <c r="M111" t="n">
-        <v>769</v>
-      </c>
+        <v>19.6931</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0.7906428571428573</v>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
         <v>110</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>45813</v>
+        <v>45874</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>NSE:SHAKTIPUMP-EQ</t>
+          <t>NSE:PARAGMILK-EQ</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5018,29 +5014,29 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>43</v>
+        <v>164</v>
       </c>
       <c r="F112" t="n">
-        <v>890.9</v>
+        <v>234.85</v>
       </c>
       <c r="G112" t="n">
-        <v>38308.7</v>
+        <v>38515.4</v>
       </c>
       <c r="H112" t="n">
-        <v>38.30869999999999</v>
+        <v>38.5154</v>
       </c>
       <c r="I112" t="n">
-        <v>19.15435</v>
+        <v>19.2577</v>
       </c>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="n">
-        <v>1582.986949999999</v>
+        <v>-2250.453100000001</v>
       </c>
       <c r="L112" t="n">
-        <v>4.473761360304893</v>
+        <v>-5.386350817822901</v>
       </c>
       <c r="M112" t="n">
-        <v>852.75</v>
+        <v>248.22</v>
       </c>
     </row>
     <row r="113">
@@ -5048,11 +5044,11 @@
         <v>111</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>45813</v>
+        <v>45874</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>NSE:WABAG-EQ</t>
+          <t>NSE:PNBGILTS-EQ</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5061,22 +5057,22 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>23</v>
+        <v>351</v>
       </c>
       <c r="F113" t="n">
-        <v>1611</v>
+        <v>106.29</v>
       </c>
       <c r="G113" t="n">
-        <v>37053</v>
+        <v>37307.79</v>
       </c>
       <c r="H113" t="n">
-        <v>37.053</v>
+        <v>37.30779</v>
       </c>
       <c r="I113" t="n">
-        <v>18.5265</v>
+        <v>18.653895</v>
       </c>
       <c r="J113" t="n">
-        <v>0.7538617887611849</v>
+        <v>0.7467777777777779</v>
       </c>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
@@ -5087,11 +5083,11 @@
         <v>112</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>45818</v>
+        <v>45874</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>NSE:PGEL-EQ</t>
+          <t>NSE:STYLEBAAZA-EQ</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5100,22 +5096,22 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>49</v>
+        <v>138</v>
       </c>
       <c r="F114" t="n">
-        <v>763.25</v>
+        <v>292.4</v>
       </c>
       <c r="G114" t="n">
-        <v>37399.25</v>
+        <v>40351.2</v>
       </c>
       <c r="H114" t="n">
-        <v>37.39925</v>
+        <v>40.3512</v>
       </c>
       <c r="I114" t="n">
-        <v>18.699625</v>
+        <v>20.1756</v>
       </c>
       <c r="J114" t="n">
-        <v>0.7527284450439228</v>
+        <v>0.8090032467532469</v>
       </c>
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
@@ -5126,11 +5122,11 @@
         <v>113</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>45826</v>
+        <v>45874</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>NSE:VISHNU-EQ</t>
+          <t>NSE:WABAG-EQ</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5139,22 +5135,22 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="F115" t="n">
-        <v>554.3</v>
+        <v>1541.3</v>
       </c>
       <c r="G115" t="n">
-        <v>39909.6</v>
+        <v>35449.9</v>
       </c>
       <c r="H115" t="n">
-        <v>39.9096</v>
+        <v>35.4499</v>
       </c>
       <c r="I115" t="n">
-        <v>19.9548</v>
+        <v>17.72495</v>
       </c>
       <c r="J115" t="n">
-        <v>0.7986302673700182</v>
+        <v>0.7326468253968256</v>
       </c>
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
@@ -5165,11 +5161,11 @@
         <v>114</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>45826</v>
+        <v>45876</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>NSE:WABAG-EQ</t>
+          <t>NSE:CUB-EQ</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5178,29 +5174,29 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>23</v>
+        <v>184</v>
       </c>
       <c r="F116" t="n">
-        <v>1523.5</v>
+        <v>215.59</v>
       </c>
       <c r="G116" t="n">
-        <v>35040.5</v>
+        <v>39668.56</v>
       </c>
       <c r="H116" t="n">
-        <v>35.0405</v>
+        <v>39.66856</v>
       </c>
       <c r="I116" t="n">
-        <v>17.52025</v>
+        <v>19.83428</v>
       </c>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="n">
-        <v>-2065.06075</v>
+        <v>-217.7428399999973</v>
       </c>
       <c r="L116" t="n">
-        <v>-5.431409062693978</v>
+        <v>-0.3973203973203905</v>
       </c>
       <c r="M116" t="n">
-        <v>1611</v>
+        <v>216.45</v>
       </c>
     </row>
     <row r="117">
@@ -5208,11 +5204,11 @@
         <v>115</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>45832</v>
+        <v>45876</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>NSE:AMBER-EQ</t>
+          <t>NSE:HUBTOWN-EQ</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -5221,29 +5217,29 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6</v>
+        <v>125</v>
       </c>
       <c r="F117" t="n">
-        <v>6731</v>
+        <v>336.75</v>
       </c>
       <c r="G117" t="n">
-        <v>40386</v>
+        <v>42093.75</v>
       </c>
       <c r="H117" t="n">
-        <v>40.386</v>
+        <v>42.09375</v>
       </c>
       <c r="I117" t="n">
-        <v>20.193</v>
+        <v>21.046875</v>
       </c>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="n">
-        <v>2360.421</v>
+        <v>5424.359374999997</v>
       </c>
       <c r="L117" t="n">
-        <v>6.37692611615962</v>
+        <v>14.99060952706163</v>
       </c>
       <c r="M117" t="n">
-        <v>6327.5</v>
+        <v>292.85</v>
       </c>
     </row>
     <row r="118">
@@ -5251,97 +5247,89 @@
         <v>116</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>45839</v>
+        <v>45876</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>NSE:PGEL-EQ</t>
+          <t>NSE:RALLIS-EQ</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="F118" t="n">
-        <v>723</v>
+        <v>365.9</v>
       </c>
       <c r="G118" t="n">
-        <v>35427</v>
+        <v>36590</v>
       </c>
       <c r="H118" t="n">
-        <v>35.427</v>
+        <v>36.59</v>
       </c>
       <c r="I118" t="n">
-        <v>17.7135</v>
-      </c>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="n">
-        <v>-2025.3905</v>
-      </c>
-      <c r="L118" t="n">
-        <v>-5.273501473960039</v>
-      </c>
-      <c r="M118" t="n">
-        <v>763.25</v>
-      </c>
+        <v>18.295</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.7390238095238095</v>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
         <v>117</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>45839</v>
+        <v>45877</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>NSE:VISHNU-EQ</t>
+          <t>NSE:REFEX-EQ</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="F119" t="n">
-        <v>524.15</v>
+        <v>414.9</v>
       </c>
       <c r="G119" t="n">
-        <v>37738.8</v>
+        <v>36511.2</v>
       </c>
       <c r="H119" t="n">
-        <v>37.7388</v>
+        <v>36.5112</v>
       </c>
       <c r="I119" t="n">
-        <v>18.8694</v>
-      </c>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="n">
-        <v>-2227.408199999998</v>
-      </c>
-      <c r="L119" t="n">
-        <v>-5.43929280173191</v>
-      </c>
-      <c r="M119" t="n">
-        <v>554.3</v>
-      </c>
+        <v>18.2556</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.7366944444444445</v>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
         <v>118</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>45882</v>
+        <v>45887</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>NSE:ZENSARTECH-EQ</t>
+          <t>NSE:SKIPPER-EQ</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -5350,22 +5338,22 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="F120" t="n">
-        <v>801.15</v>
+        <v>534.1</v>
       </c>
       <c r="G120" t="n">
-        <v>37654.05</v>
+        <v>37921.1</v>
       </c>
       <c r="H120" t="n">
-        <v>37.65405</v>
+        <v>37.9211</v>
       </c>
       <c r="I120" t="n">
-        <v>18.827025</v>
+        <v>18.96055</v>
       </c>
       <c r="J120" t="n">
-        <v>0.7626735723081708</v>
+        <v>0.761047619047619</v>
       </c>
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr"/>
@@ -5376,39 +5364,82 @@
         <v>119</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>45883</v>
+        <v>45888</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>NSE:SAPPHIRE-EQ</t>
+          <t>NSE:REFEX-EQ</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>127</v>
+        <v>88</v>
       </c>
       <c r="F121" t="n">
-        <v>306.3</v>
+        <v>382.65</v>
       </c>
       <c r="G121" t="n">
-        <v>38900.1</v>
+        <v>33673.2</v>
       </c>
       <c r="H121" t="n">
-        <v>38.9001</v>
+        <v>33.67319999999999</v>
       </c>
       <c r="I121" t="n">
-        <v>19.45005</v>
-      </c>
-      <c r="J121" t="n">
-        <v>0.7801137434759181</v>
-      </c>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr"/>
+        <v>16.8366</v>
+      </c>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="n">
+        <v>-2888.5098</v>
+      </c>
+      <c r="L121" t="n">
+        <v>-7.77295733911786</v>
+      </c>
+      <c r="M121" t="n">
+        <v>414.9</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="B122" s="2" t="n">
+        <v>45888</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>NSE:SARDAEN-EQ</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>65</v>
+      </c>
+      <c r="F122" t="n">
+        <v>590.55</v>
+      </c>
+      <c r="G122" t="n">
+        <v>38385.75</v>
+      </c>
+      <c r="H122" t="n">
+        <v>38.38575</v>
+      </c>
+      <c r="I122" t="n">
+        <v>19.192875</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.7683333333333333</v>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
